--- a/source/STC_Textblocs_Source.xlsx
+++ b/source/STC_Textblocs_Source.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stctravel-my.sharepoint.com/personal/clemens_bartlome_stc_ch/Documents/12_Development/github/TextblocsOutlook/TextblocsOutlookAddIn/src/source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stctravel-my.sharepoint.com/personal/clemens_bartlome_stc_ch/Documents/12_Development/github/TextblocsOutlook/TextblocsOutlookAddIn/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{94B17F8A-FB08-44EE-9220-44A499DEE7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85D9299D-0CDF-497C-8193-38F66D4B8684}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{94B17F8A-FB08-44EE-9220-44A499DEE7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C2BFAFE-85DF-4688-9589-7DFF87174B14}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99471E66-6148-4C96-BA12-0B3DC411200A}"/>
   </bookViews>
@@ -2928,7 +2928,8 @@
 Cordiali saluti</t>
   </si>
   <si>
-    <t>Grüezi
+    <r>
+      <t xml:space="preserve">Grüezi
 Vielen Dank für Ihre Anfrage und Ihr Interesse an unseren Angeboten. Es freut uns sehr, Sie bei der Planung Ihrer Ferien in der Schweiz unterstützen zu dürfen.
 Über den folgenden Link können Sie Ihr persönliches Reiseprogramm bequem einsehen: ==Link==
 **Inkludierte Leistungen:**
@@ -2940,13 +2941,31 @@
 **Warum bei uns buchen?**
 Als spezialisierter Anbieter für Schweiz-Reisen stellen wir für Sie sorgfältig abgestimmte Reiseprogramme zusammen – perfekt organisiert und individuell auf Ihre Wünsche zugeschnitten. So profitieren Sie von einer einfachen, zuverlässigen und professionellen Reiseplanung aus einer Hand.
 **Sichern Sie sich jetzt Ihr Wunschprogramm**
-Ihr aktuelles Angebot wurde individuell für Sie zusammengestellt und basiert auf den derzeit verfügbaren Kontingenten. Besonders gefragte Leistungen wie Panoramazüge und ausgewählte Hotels sind oft schnell ausgebucht. Mit einer frühzeitigen Bestätigung stellen Sie sicher, dass Ihre Reise genau wie geplant umgesetzt werden kann.
+Ihr aktuelles Angebot wurde individuell für Sie zusammengestellt und basiert auf den derzeit verfügbaren Kontingenten. Besonders gefragte Leistungen wie </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">**Panoramazüge** </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>und ausgewählte Hotels sind oft schnell ausgebucht. Mit einer frühzeitigen Bestätigung stellen Sie sicher, dass Ihre Reise genau wie geplant umgesetzt werden kann.
 **Sichern Sie sich Ihre Reise, indem Sie Ihre Offerte (==Link==) verbindlich bestätigen.**
 Bitte teilen Sie uns bis spätestens ==23. April 2026== mit, ob das Angebot Ihren Vorstellungen entspricht.
 Hier finden Sie ausserdem unsere [allgemeinen Vertragsbedingungen](https://switzerlandtravelcentre.com/de-ch/agb) sowie Antworten auf [häufige Fragen](https://switzerlandtravelcentre.com/de-ch/reiseinfos/haeufige-fragen).
 Falls Sie weitere Fragen haben oder Anpassungen wünschen, lassen Sie es uns einfach wissen – wir helfen Ihnen gerne weiter.
 Wir freuen uns auf Ihre Rückmeldung und wünschen Ihnen einen schönen Tag.
 Freundliche Grüsse</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3582,220 +3601,220 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -4135,8 +4154,8 @@
   <dimension ref="A1:H483"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="144" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" style="144" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" style="143" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" style="143" customWidth="1"/>
     <col min="3" max="3" width="61.28515625" customWidth="1"/>
     <col min="4" max="4" width="46.42578125" customWidth="1"/>
     <col min="5" max="5" width="54.42578125" customWidth="1"/>
@@ -4968,7 +4987,7 @@
       <c r="A42" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="B42" s="75" t="s">
+      <c r="B42" s="145" t="s">
         <v>207</v>
       </c>
       <c r="C42" s="69" t="s">
@@ -4985,12 +5004,12 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="76"/>
-      <c r="B43" s="75"/>
+      <c r="A43" s="75"/>
+      <c r="B43" s="145"/>
       <c r="C43" s="69" t="s">
         <v>212</v>
       </c>
-      <c r="D43" s="77" t="s">
+      <c r="D43" s="76" t="s">
         <v>213</v>
       </c>
       <c r="E43" s="69" t="s">
@@ -5004,7 +5023,7 @@
       <c r="A44" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="B44" s="78" t="s">
+      <c r="B44" s="77" t="s">
         <v>216</v>
       </c>
       <c r="C44" s="73" t="s">
@@ -5024,19 +5043,19 @@
       <c r="A45" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="B45" s="79" t="s">
+      <c r="B45" s="78" t="s">
         <v>221</v>
       </c>
-      <c r="C45" s="80" t="s">
+      <c r="C45" s="79" t="s">
         <v>222</v>
       </c>
-      <c r="D45" s="81" t="s">
+      <c r="D45" s="80" t="s">
         <v>223</v>
       </c>
-      <c r="E45" s="80" t="s">
+      <c r="E45" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="82" t="s">
+      <c r="F45" s="81" t="s">
         <v>225</v>
       </c>
     </row>
@@ -5044,7 +5063,7 @@
       <c r="A46" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="B46" s="78" t="s">
+      <c r="B46" s="77" t="s">
         <v>226</v>
       </c>
       <c r="C46" s="73" t="s">
@@ -5064,7 +5083,7 @@
       <c r="A47" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="B47" s="79" t="s">
+      <c r="B47" s="78" t="s">
         <v>231</v>
       </c>
       <c r="C47" s="69" t="s">
@@ -5084,7 +5103,7 @@
       <c r="A48" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="B48" s="78" t="s">
+      <c r="B48" s="77" t="s">
         <v>236</v>
       </c>
       <c r="C48" s="73" t="s">
@@ -5104,7 +5123,7 @@
       <c r="A49" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="B49" s="79" t="s">
+      <c r="B49" s="78" t="s">
         <v>241</v>
       </c>
       <c r="C49" s="69" t="s">
@@ -5124,13 +5143,13 @@
       <c r="A50" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="B50" s="78" t="s">
+      <c r="B50" s="77" t="s">
         <v>246</v>
       </c>
       <c r="C50" s="73" t="s">
         <v>247</v>
       </c>
-      <c r="D50" s="83" t="s">
+      <c r="D50" s="82" t="s">
         <v>248</v>
       </c>
       <c r="E50" s="73" t="s">
@@ -5144,13 +5163,13 @@
       <c r="A51" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="B51" s="79" t="s">
+      <c r="B51" s="78" t="s">
         <v>251</v>
       </c>
       <c r="C51" s="69" t="s">
         <v>150</v>
       </c>
-      <c r="D51" s="84" t="s">
+      <c r="D51" s="83" t="s">
         <v>150</v>
       </c>
       <c r="E51" s="69" t="s">
@@ -5164,7 +5183,7 @@
       <c r="A52" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B52" s="85" t="s">
+      <c r="B52" s="84" t="s">
         <v>254</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -5204,19 +5223,19 @@
       <c r="A54" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B54" s="86" t="s">
+      <c r="B54" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="C54" s="87" t="s">
+      <c r="C54" s="86" t="s">
         <v>265</v>
       </c>
-      <c r="D54" s="87" t="s">
+      <c r="D54" s="86" t="s">
         <v>266</v>
       </c>
-      <c r="E54" s="87" t="s">
+      <c r="E54" s="86" t="s">
         <v>267</v>
       </c>
-      <c r="F54" s="88" t="s">
+      <c r="F54" s="87" t="s">
         <v>268</v>
       </c>
     </row>
@@ -5224,7 +5243,7 @@
       <c r="A55" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B55" s="89" t="s">
+      <c r="B55" s="88" t="s">
         <v>269</v>
       </c>
       <c r="C55" s="8" t="s">
@@ -5244,19 +5263,19 @@
       <c r="A56" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B56" s="90" t="s">
+      <c r="B56" s="89" t="s">
         <v>274</v>
       </c>
-      <c r="C56" s="87" t="s">
+      <c r="C56" s="86" t="s">
         <v>275</v>
       </c>
-      <c r="D56" s="87" t="s">
+      <c r="D56" s="86" t="s">
         <v>276</v>
       </c>
-      <c r="E56" s="87" t="s">
+      <c r="E56" s="86" t="s">
         <v>277</v>
       </c>
-      <c r="F56" s="88" t="s">
+      <c r="F56" s="87" t="s">
         <v>278</v>
       </c>
     </row>
@@ -5284,19 +5303,19 @@
       <c r="A58" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B58" s="86" t="s">
+      <c r="B58" s="85" t="s">
         <v>284</v>
       </c>
-      <c r="C58" s="87" t="s">
+      <c r="C58" s="86" t="s">
         <v>285</v>
       </c>
-      <c r="D58" s="91" t="s">
+      <c r="D58" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="E58" s="91" t="s">
+      <c r="E58" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="F58" s="92" t="s">
+      <c r="F58" s="91" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5304,7 +5323,7 @@
       <c r="A59" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="B59" s="93" t="s">
+      <c r="B59" s="92" t="s">
         <v>287</v>
       </c>
       <c r="C59" s="15" t="s">
@@ -5324,7 +5343,7 @@
       <c r="A60" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="B60" s="94" t="s">
+      <c r="B60" s="93" t="s">
         <v>292</v>
       </c>
       <c r="C60" s="18" t="s">
@@ -5344,7 +5363,7 @@
       <c r="A61" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="B61" s="95" t="s">
+      <c r="B61" s="94" t="s">
         <v>297</v>
       </c>
       <c r="C61" s="21" t="s">
@@ -5364,7 +5383,7 @@
       <c r="A62" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="B62" s="94" t="s">
+      <c r="B62" s="93" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="18" t="s">
@@ -5381,122 +5400,122 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="96" t="s">
+      <c r="A63" s="95" t="s">
         <v>307</v>
       </c>
-      <c r="B63" s="97" t="s">
+      <c r="B63" s="96" t="s">
         <v>308</v>
       </c>
-      <c r="C63" s="98" t="s">
+      <c r="C63" s="97" t="s">
         <v>309</v>
       </c>
-      <c r="D63" s="98" t="s">
+      <c r="D63" s="97" t="s">
         <v>310</v>
       </c>
-      <c r="E63" s="98" t="s">
+      <c r="E63" s="97" t="s">
         <v>311</v>
       </c>
-      <c r="F63" s="99" t="s">
+      <c r="F63" s="98" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="96" t="s">
+      <c r="A64" s="95" t="s">
         <v>307</v>
       </c>
-      <c r="B64" s="100" t="s">
+      <c r="B64" s="99" t="s">
         <v>313</v>
       </c>
-      <c r="C64" s="101" t="s">
+      <c r="C64" s="100" t="s">
         <v>314</v>
       </c>
-      <c r="D64" s="101" t="s">
+      <c r="D64" s="100" t="s">
         <v>315</v>
       </c>
-      <c r="E64" s="101" t="s">
+      <c r="E64" s="100" t="s">
         <v>316</v>
       </c>
-      <c r="F64" s="102" t="s">
+      <c r="F64" s="101" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="96" t="s">
+      <c r="A65" s="95" t="s">
         <v>307</v>
       </c>
-      <c r="B65" s="103" t="s">
+      <c r="B65" s="102" t="s">
         <v>318</v>
       </c>
-      <c r="C65" s="104" t="s">
+      <c r="C65" s="103" t="s">
         <v>319</v>
       </c>
-      <c r="D65" s="105" t="s">
+      <c r="D65" s="104" t="s">
         <v>320</v>
       </c>
-      <c r="E65" s="105" t="s">
+      <c r="E65" s="104" t="s">
         <v>321</v>
       </c>
-      <c r="F65" s="106" t="s">
+      <c r="F65" s="105" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="175.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="96" t="s">
+      <c r="A66" s="95" t="s">
         <v>307</v>
       </c>
-      <c r="B66" s="107" t="s">
+      <c r="B66" s="106" t="s">
         <v>323</v>
       </c>
-      <c r="C66" s="108" t="s">
+      <c r="C66" s="107" t="s">
         <v>324</v>
       </c>
-      <c r="D66" s="108" t="s">
+      <c r="D66" s="107" t="s">
         <v>325</v>
       </c>
-      <c r="E66" s="108" t="s">
+      <c r="E66" s="107" t="s">
         <v>326</v>
       </c>
-      <c r="F66" s="109" t="s">
+      <c r="F66" s="108" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="110" t="s">
+      <c r="A67" s="109" t="s">
         <v>328</v>
       </c>
-      <c r="B67" s="111" t="s">
+      <c r="B67" s="110" t="s">
         <v>329</v>
       </c>
-      <c r="C67" s="112" t="s">
+      <c r="C67" s="111" t="s">
         <v>330</v>
       </c>
-      <c r="D67" s="113" t="s">
+      <c r="D67" s="112" t="s">
         <v>331</v>
       </c>
-      <c r="E67" s="113" t="s">
+      <c r="E67" s="112" t="s">
         <v>332</v>
       </c>
-      <c r="F67" s="114" t="s">
+      <c r="F67" s="113" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="110" t="s">
+      <c r="A68" s="109" t="s">
         <v>328</v>
       </c>
-      <c r="B68" s="115" t="s">
+      <c r="B68" s="114" t="s">
         <v>334</v>
       </c>
-      <c r="C68" s="116" t="s">
+      <c r="C68" s="115" t="s">
         <v>335</v>
       </c>
-      <c r="D68" s="117" t="s">
+      <c r="D68" s="116" t="s">
         <v>336</v>
       </c>
-      <c r="E68" s="117" t="s">
+      <c r="E68" s="116" t="s">
         <v>337</v>
       </c>
-      <c r="F68" s="118" t="s">
+      <c r="F68" s="117" t="s">
         <v>338</v>
       </c>
     </row>
@@ -5504,19 +5523,19 @@
       <c r="A69" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B69" s="85" t="s">
+      <c r="B69" s="84" t="s">
         <v>340</v>
       </c>
-      <c r="C69" s="119" t="s">
+      <c r="C69" s="118" t="s">
         <v>341</v>
       </c>
-      <c r="D69" s="119" t="s">
+      <c r="D69" s="118" t="s">
         <v>342</v>
       </c>
-      <c r="E69" s="119" t="s">
+      <c r="E69" s="118" t="s">
         <v>343</v>
       </c>
-      <c r="F69" s="120" t="s">
+      <c r="F69" s="119" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5524,67 +5543,67 @@
       <c r="A70" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B70" s="121" t="s">
+      <c r="B70" s="120" t="s">
         <v>345</v>
       </c>
-      <c r="C70" s="122" t="s">
+      <c r="C70" s="121" t="s">
         <v>346</v>
       </c>
-      <c r="D70" s="122" t="s">
+      <c r="D70" s="121" t="s">
         <v>347</v>
       </c>
-      <c r="E70" s="122" t="s">
+      <c r="E70" s="121" t="s">
         <v>348</v>
       </c>
-      <c r="F70" s="123" t="s">
+      <c r="F70" s="122" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="124"/>
-      <c r="B71" s="121"/>
-      <c r="C71" s="122"/>
-      <c r="D71" s="122"/>
-      <c r="E71" s="122"/>
-      <c r="F71" s="123"/>
+      <c r="A71" s="123"/>
+      <c r="B71" s="120"/>
+      <c r="C71" s="121"/>
+      <c r="D71" s="121"/>
+      <c r="E71" s="121"/>
+      <c r="F71" s="122"/>
     </row>
     <row r="72" spans="1:6" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B72" s="125" t="s">
+      <c r="B72" s="124" t="s">
         <v>350</v>
       </c>
-      <c r="C72" s="126" t="s">
+      <c r="C72" s="125" t="s">
         <v>351</v>
       </c>
-      <c r="D72" s="126" t="s">
+      <c r="D72" s="125" t="s">
         <v>352</v>
       </c>
-      <c r="E72" s="126" t="s">
+      <c r="E72" s="125" t="s">
         <v>353</v>
       </c>
-      <c r="F72" s="127" t="s">
+      <c r="F72" s="126" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="281.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="128" t="s">
+      <c r="A73" s="127" t="s">
         <v>355</v>
       </c>
-      <c r="B73" s="129" t="s">
+      <c r="B73" s="128" t="s">
         <v>356</v>
       </c>
-      <c r="C73" s="130" t="s">
+      <c r="C73" s="129" t="s">
         <v>357</v>
       </c>
-      <c r="D73" s="130" t="s">
+      <c r="D73" s="129" t="s">
         <v>358</v>
       </c>
-      <c r="E73" s="130" t="s">
+      <c r="E73" s="129" t="s">
         <v>359</v>
       </c>
-      <c r="F73" s="131" t="s">
+      <c r="F73" s="130" t="s">
         <v>360</v>
       </c>
     </row>
@@ -5592,19 +5611,19 @@
       <c r="A74" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="B74" s="132" t="s">
+      <c r="B74" s="131" t="s">
         <v>362</v>
       </c>
-      <c r="C74" s="133" t="s">
+      <c r="C74" s="132" t="s">
         <v>363</v>
       </c>
-      <c r="D74" s="133" t="s">
+      <c r="D74" s="132" t="s">
         <v>364</v>
       </c>
-      <c r="E74" s="133" t="s">
+      <c r="E74" s="132" t="s">
         <v>365</v>
       </c>
-      <c r="F74" s="134" t="s">
+      <c r="F74" s="133" t="s">
         <v>366</v>
       </c>
     </row>
@@ -5612,19 +5631,19 @@
       <c r="A75" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="B75" s="135" t="s">
+      <c r="B75" s="134" t="s">
         <v>367</v>
       </c>
-      <c r="C75" s="136" t="s">
+      <c r="C75" s="135" t="s">
         <v>368</v>
       </c>
-      <c r="D75" s="136" t="s">
+      <c r="D75" s="135" t="s">
         <v>369</v>
       </c>
-      <c r="E75" s="137" t="s">
+      <c r="E75" s="136" t="s">
         <v>370</v>
       </c>
-      <c r="F75" s="138" t="s">
+      <c r="F75" s="137" t="s">
         <v>371</v>
       </c>
     </row>
@@ -5632,2454 +5651,2454 @@
       <c r="A76" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="B76" s="139" t="s">
+      <c r="B76" s="138" t="s">
         <v>372</v>
       </c>
-      <c r="C76" s="140" t="s">
+      <c r="C76" s="139" t="s">
         <v>373</v>
       </c>
-      <c r="D76" s="141" t="s">
+      <c r="D76" s="140" t="s">
         <v>374</v>
       </c>
-      <c r="E76" s="142" t="s">
+      <c r="E76" s="141" t="s">
         <v>375</v>
       </c>
-      <c r="F76" s="143" t="s">
+      <c r="F76" s="142" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C77" s="145"/>
-      <c r="D77" s="145"/>
-      <c r="E77" s="145"/>
-      <c r="F77" s="145"/>
+      <c r="C77" s="144"/>
+      <c r="D77" s="144"/>
+      <c r="E77" s="144"/>
+      <c r="F77" s="144"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C78" s="145"/>
-      <c r="D78" s="145"/>
-      <c r="E78" s="145"/>
-      <c r="F78" s="145"/>
+      <c r="C78" s="144"/>
+      <c r="D78" s="144"/>
+      <c r="E78" s="144"/>
+      <c r="F78" s="144"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C79" s="145"/>
-      <c r="D79" s="145"/>
-      <c r="E79" s="145"/>
-      <c r="F79" s="145"/>
+      <c r="C79" s="144"/>
+      <c r="D79" s="144"/>
+      <c r="E79" s="144"/>
+      <c r="F79" s="144"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C80" s="145"/>
-      <c r="D80" s="145"/>
-      <c r="E80" s="145"/>
-      <c r="F80" s="145"/>
+      <c r="C80" s="144"/>
+      <c r="D80" s="144"/>
+      <c r="E80" s="144"/>
+      <c r="F80" s="144"/>
     </row>
     <row r="81" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C81" s="145"/>
-      <c r="D81" s="145"/>
-      <c r="E81" s="145"/>
-      <c r="F81" s="145"/>
+      <c r="C81" s="144"/>
+      <c r="D81" s="144"/>
+      <c r="E81" s="144"/>
+      <c r="F81" s="144"/>
     </row>
     <row r="82" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C82" s="145"/>
-      <c r="D82" s="145"/>
-      <c r="E82" s="145"/>
-      <c r="F82" s="145"/>
+      <c r="C82" s="144"/>
+      <c r="D82" s="144"/>
+      <c r="E82" s="144"/>
+      <c r="F82" s="144"/>
     </row>
     <row r="83" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C83" s="145"/>
-      <c r="D83" s="145"/>
-      <c r="E83" s="145"/>
-      <c r="F83" s="145"/>
+      <c r="C83" s="144"/>
+      <c r="D83" s="144"/>
+      <c r="E83" s="144"/>
+      <c r="F83" s="144"/>
     </row>
     <row r="84" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C84" s="145"/>
-      <c r="D84" s="145"/>
-      <c r="E84" s="145"/>
-      <c r="F84" s="145"/>
+      <c r="C84" s="144"/>
+      <c r="D84" s="144"/>
+      <c r="E84" s="144"/>
+      <c r="F84" s="144"/>
     </row>
     <row r="85" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C85" s="145"/>
-      <c r="D85" s="145"/>
-      <c r="E85" s="145"/>
-      <c r="F85" s="145"/>
+      <c r="C85" s="144"/>
+      <c r="D85" s="144"/>
+      <c r="E85" s="144"/>
+      <c r="F85" s="144"/>
     </row>
     <row r="86" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C86" s="145"/>
-      <c r="D86" s="145"/>
-      <c r="E86" s="145"/>
-      <c r="F86" s="145"/>
+      <c r="C86" s="144"/>
+      <c r="D86" s="144"/>
+      <c r="E86" s="144"/>
+      <c r="F86" s="144"/>
     </row>
     <row r="87" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C87" s="145"/>
-      <c r="D87" s="145"/>
-      <c r="E87" s="145"/>
-      <c r="F87" s="145"/>
+      <c r="C87" s="144"/>
+      <c r="D87" s="144"/>
+      <c r="E87" s="144"/>
+      <c r="F87" s="144"/>
     </row>
     <row r="88" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="F88" s="145"/>
+      <c r="F88" s="144"/>
     </row>
     <row r="89" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="F89" s="145"/>
+      <c r="F89" s="144"/>
     </row>
     <row r="90" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="F90" s="145"/>
+      <c r="F90" s="144"/>
     </row>
     <row r="91" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C91" s="145"/>
-      <c r="D91" s="145"/>
-      <c r="E91" s="145"/>
-      <c r="F91" s="145"/>
+      <c r="C91" s="144"/>
+      <c r="D91" s="144"/>
+      <c r="E91" s="144"/>
+      <c r="F91" s="144"/>
     </row>
     <row r="92" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C92" s="145"/>
-      <c r="D92" s="145"/>
-      <c r="E92" s="145"/>
-      <c r="F92" s="145"/>
+      <c r="C92" s="144"/>
+      <c r="D92" s="144"/>
+      <c r="E92" s="144"/>
+      <c r="F92" s="144"/>
     </row>
     <row r="93" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C93" s="145"/>
-      <c r="D93" s="145"/>
-      <c r="E93" s="145"/>
-      <c r="F93" s="145"/>
+      <c r="C93" s="144"/>
+      <c r="D93" s="144"/>
+      <c r="E93" s="144"/>
+      <c r="F93" s="144"/>
     </row>
     <row r="94" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C94" s="145"/>
-      <c r="D94" s="145"/>
-      <c r="E94" s="145"/>
-      <c r="F94" s="145"/>
+      <c r="C94" s="144"/>
+      <c r="D94" s="144"/>
+      <c r="E94" s="144"/>
+      <c r="F94" s="144"/>
     </row>
     <row r="95" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C95" s="145"/>
-      <c r="D95" s="145"/>
-      <c r="E95" s="145"/>
-      <c r="F95" s="145"/>
+      <c r="C95" s="144"/>
+      <c r="D95" s="144"/>
+      <c r="E95" s="144"/>
+      <c r="F95" s="144"/>
     </row>
     <row r="96" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C96" s="145"/>
-      <c r="D96" s="145"/>
-      <c r="E96" s="145"/>
-      <c r="F96" s="145"/>
+      <c r="C96" s="144"/>
+      <c r="D96" s="144"/>
+      <c r="E96" s="144"/>
+      <c r="F96" s="144"/>
     </row>
     <row r="97" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C97" s="145"/>
-      <c r="D97" s="145"/>
-      <c r="E97" s="145"/>
-      <c r="F97" s="145"/>
+      <c r="C97" s="144"/>
+      <c r="D97" s="144"/>
+      <c r="E97" s="144"/>
+      <c r="F97" s="144"/>
     </row>
     <row r="98" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C98" s="145"/>
-      <c r="D98" s="145"/>
-      <c r="E98" s="145"/>
-      <c r="F98" s="145"/>
+      <c r="C98" s="144"/>
+      <c r="D98" s="144"/>
+      <c r="E98" s="144"/>
+      <c r="F98" s="144"/>
     </row>
     <row r="99" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C99" s="145"/>
-      <c r="D99" s="145"/>
-      <c r="E99" s="145"/>
-      <c r="F99" s="145"/>
+      <c r="C99" s="144"/>
+      <c r="D99" s="144"/>
+      <c r="E99" s="144"/>
+      <c r="F99" s="144"/>
     </row>
     <row r="100" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C100" s="145"/>
-      <c r="D100" s="145"/>
-      <c r="E100" s="145"/>
-      <c r="F100" s="145"/>
+      <c r="C100" s="144"/>
+      <c r="D100" s="144"/>
+      <c r="E100" s="144"/>
+      <c r="F100" s="144"/>
     </row>
     <row r="101" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C101" s="145"/>
-      <c r="D101" s="145"/>
-      <c r="E101" s="145"/>
-      <c r="F101" s="145"/>
+      <c r="C101" s="144"/>
+      <c r="D101" s="144"/>
+      <c r="E101" s="144"/>
+      <c r="F101" s="144"/>
     </row>
     <row r="102" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C102" s="145"/>
-      <c r="D102" s="145"/>
-      <c r="E102" s="145"/>
-      <c r="F102" s="145"/>
+      <c r="C102" s="144"/>
+      <c r="D102" s="144"/>
+      <c r="E102" s="144"/>
+      <c r="F102" s="144"/>
     </row>
     <row r="103" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C103" s="145"/>
-      <c r="D103" s="145"/>
-      <c r="E103" s="145"/>
-      <c r="F103" s="145"/>
+      <c r="C103" s="144"/>
+      <c r="D103" s="144"/>
+      <c r="E103" s="144"/>
+      <c r="F103" s="144"/>
     </row>
     <row r="104" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C104" s="145"/>
-      <c r="D104" s="145"/>
-      <c r="E104" s="145"/>
-      <c r="F104" s="145"/>
+      <c r="C104" s="144"/>
+      <c r="D104" s="144"/>
+      <c r="E104" s="144"/>
+      <c r="F104" s="144"/>
     </row>
     <row r="105" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C105" s="145"/>
-      <c r="D105" s="145"/>
-      <c r="E105" s="145"/>
-      <c r="F105" s="145"/>
+      <c r="C105" s="144"/>
+      <c r="D105" s="144"/>
+      <c r="E105" s="144"/>
+      <c r="F105" s="144"/>
     </row>
     <row r="106" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C106" s="145"/>
-      <c r="D106" s="145"/>
-      <c r="E106" s="145"/>
-      <c r="F106" s="145"/>
+      <c r="C106" s="144"/>
+      <c r="D106" s="144"/>
+      <c r="E106" s="144"/>
+      <c r="F106" s="144"/>
     </row>
     <row r="107" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C107" s="145"/>
-      <c r="D107" s="145"/>
-      <c r="E107" s="145"/>
-      <c r="F107" s="145"/>
+      <c r="C107" s="144"/>
+      <c r="D107" s="144"/>
+      <c r="E107" s="144"/>
+      <c r="F107" s="144"/>
     </row>
     <row r="108" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C108" s="145"/>
-      <c r="D108" s="145"/>
-      <c r="E108" s="145"/>
-      <c r="F108" s="145"/>
+      <c r="C108" s="144"/>
+      <c r="D108" s="144"/>
+      <c r="E108" s="144"/>
+      <c r="F108" s="144"/>
     </row>
     <row r="109" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C109" s="145"/>
-      <c r="D109" s="145"/>
-      <c r="E109" s="145"/>
-      <c r="F109" s="145"/>
+      <c r="C109" s="144"/>
+      <c r="D109" s="144"/>
+      <c r="E109" s="144"/>
+      <c r="F109" s="144"/>
     </row>
     <row r="110" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C110" s="145"/>
-      <c r="D110" s="145"/>
-      <c r="E110" s="145"/>
-      <c r="F110" s="145"/>
+      <c r="C110" s="144"/>
+      <c r="D110" s="144"/>
+      <c r="E110" s="144"/>
+      <c r="F110" s="144"/>
     </row>
     <row r="111" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C111" s="145"/>
-      <c r="D111" s="145"/>
-      <c r="E111" s="145"/>
-      <c r="F111" s="145"/>
+      <c r="C111" s="144"/>
+      <c r="D111" s="144"/>
+      <c r="E111" s="144"/>
+      <c r="F111" s="144"/>
     </row>
     <row r="112" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C112" s="145"/>
-      <c r="D112" s="145"/>
-      <c r="E112" s="145"/>
-      <c r="F112" s="145"/>
+      <c r="C112" s="144"/>
+      <c r="D112" s="144"/>
+      <c r="E112" s="144"/>
+      <c r="F112" s="144"/>
     </row>
     <row r="113" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C113" s="145"/>
-      <c r="D113" s="145"/>
-      <c r="E113" s="145"/>
-      <c r="F113" s="145"/>
+      <c r="C113" s="144"/>
+      <c r="D113" s="144"/>
+      <c r="E113" s="144"/>
+      <c r="F113" s="144"/>
     </row>
     <row r="114" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C114" s="145"/>
-      <c r="D114" s="145"/>
-      <c r="E114" s="145"/>
-      <c r="F114" s="145"/>
+      <c r="C114" s="144"/>
+      <c r="D114" s="144"/>
+      <c r="E114" s="144"/>
+      <c r="F114" s="144"/>
     </row>
     <row r="115" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C115" s="145"/>
-      <c r="D115" s="145"/>
-      <c r="E115" s="145"/>
-      <c r="F115" s="145"/>
+      <c r="C115" s="144"/>
+      <c r="D115" s="144"/>
+      <c r="E115" s="144"/>
+      <c r="F115" s="144"/>
     </row>
     <row r="116" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C116" s="145"/>
-      <c r="D116" s="145"/>
-      <c r="E116" s="145"/>
-      <c r="F116" s="145"/>
+      <c r="C116" s="144"/>
+      <c r="D116" s="144"/>
+      <c r="E116" s="144"/>
+      <c r="F116" s="144"/>
     </row>
     <row r="117" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C117" s="145"/>
-      <c r="D117" s="145"/>
-      <c r="E117" s="145"/>
-      <c r="F117" s="145"/>
+      <c r="C117" s="144"/>
+      <c r="D117" s="144"/>
+      <c r="E117" s="144"/>
+      <c r="F117" s="144"/>
     </row>
     <row r="118" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C118" s="145"/>
-      <c r="D118" s="145"/>
-      <c r="E118" s="145"/>
-      <c r="F118" s="145"/>
+      <c r="C118" s="144"/>
+      <c r="D118" s="144"/>
+      <c r="E118" s="144"/>
+      <c r="F118" s="144"/>
     </row>
     <row r="119" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C119" s="145"/>
-      <c r="D119" s="145"/>
-      <c r="E119" s="145"/>
-      <c r="F119" s="145"/>
+      <c r="C119" s="144"/>
+      <c r="D119" s="144"/>
+      <c r="E119" s="144"/>
+      <c r="F119" s="144"/>
     </row>
     <row r="120" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C120" s="145"/>
-      <c r="D120" s="145"/>
-      <c r="E120" s="145"/>
-      <c r="F120" s="145"/>
+      <c r="C120" s="144"/>
+      <c r="D120" s="144"/>
+      <c r="E120" s="144"/>
+      <c r="F120" s="144"/>
     </row>
     <row r="121" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C121" s="145"/>
-      <c r="D121" s="145"/>
-      <c r="E121" s="145"/>
-      <c r="F121" s="145"/>
+      <c r="C121" s="144"/>
+      <c r="D121" s="144"/>
+      <c r="E121" s="144"/>
+      <c r="F121" s="144"/>
     </row>
     <row r="122" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C122" s="145"/>
-      <c r="D122" s="145"/>
-      <c r="E122" s="145"/>
-      <c r="F122" s="145"/>
+      <c r="C122" s="144"/>
+      <c r="D122" s="144"/>
+      <c r="E122" s="144"/>
+      <c r="F122" s="144"/>
     </row>
     <row r="123" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C123" s="145"/>
-      <c r="D123" s="145"/>
-      <c r="E123" s="145"/>
-      <c r="F123" s="145"/>
+      <c r="C123" s="144"/>
+      <c r="D123" s="144"/>
+      <c r="E123" s="144"/>
+      <c r="F123" s="144"/>
     </row>
     <row r="124" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C124" s="145"/>
-      <c r="D124" s="145"/>
-      <c r="E124" s="145"/>
-      <c r="F124" s="145"/>
+      <c r="C124" s="144"/>
+      <c r="D124" s="144"/>
+      <c r="E124" s="144"/>
+      <c r="F124" s="144"/>
     </row>
     <row r="125" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C125" s="145"/>
-      <c r="D125" s="145"/>
-      <c r="E125" s="145"/>
-      <c r="F125" s="145"/>
+      <c r="C125" s="144"/>
+      <c r="D125" s="144"/>
+      <c r="E125" s="144"/>
+      <c r="F125" s="144"/>
     </row>
     <row r="126" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C126" s="145"/>
-      <c r="D126" s="145"/>
-      <c r="E126" s="145"/>
-      <c r="F126" s="145"/>
+      <c r="C126" s="144"/>
+      <c r="D126" s="144"/>
+      <c r="E126" s="144"/>
+      <c r="F126" s="144"/>
     </row>
     <row r="127" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C127" s="145"/>
-      <c r="D127" s="145"/>
-      <c r="E127" s="145"/>
-      <c r="F127" s="145"/>
+      <c r="C127" s="144"/>
+      <c r="D127" s="144"/>
+      <c r="E127" s="144"/>
+      <c r="F127" s="144"/>
     </row>
     <row r="128" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C128" s="145"/>
-      <c r="D128" s="145"/>
-      <c r="E128" s="145"/>
-      <c r="F128" s="145"/>
+      <c r="C128" s="144"/>
+      <c r="D128" s="144"/>
+      <c r="E128" s="144"/>
+      <c r="F128" s="144"/>
     </row>
     <row r="129" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C129" s="145"/>
-      <c r="D129" s="145"/>
-      <c r="E129" s="145"/>
-      <c r="F129" s="145"/>
+      <c r="C129" s="144"/>
+      <c r="D129" s="144"/>
+      <c r="E129" s="144"/>
+      <c r="F129" s="144"/>
     </row>
     <row r="130" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C130" s="145"/>
-      <c r="D130" s="145"/>
-      <c r="E130" s="145"/>
-      <c r="F130" s="145"/>
+      <c r="C130" s="144"/>
+      <c r="D130" s="144"/>
+      <c r="E130" s="144"/>
+      <c r="F130" s="144"/>
     </row>
     <row r="131" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C131" s="145"/>
-      <c r="D131" s="145"/>
-      <c r="E131" s="145"/>
-      <c r="F131" s="145"/>
+      <c r="C131" s="144"/>
+      <c r="D131" s="144"/>
+      <c r="E131" s="144"/>
+      <c r="F131" s="144"/>
     </row>
     <row r="132" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C132" s="145"/>
-      <c r="D132" s="145"/>
-      <c r="E132" s="145"/>
-      <c r="F132" s="145"/>
+      <c r="C132" s="144"/>
+      <c r="D132" s="144"/>
+      <c r="E132" s="144"/>
+      <c r="F132" s="144"/>
     </row>
     <row r="133" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C133" s="145"/>
-      <c r="D133" s="145"/>
-      <c r="E133" s="145"/>
-      <c r="F133" s="145"/>
+      <c r="C133" s="144"/>
+      <c r="D133" s="144"/>
+      <c r="E133" s="144"/>
+      <c r="F133" s="144"/>
     </row>
     <row r="134" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C134" s="145"/>
-      <c r="D134" s="145"/>
-      <c r="E134" s="145"/>
-      <c r="F134" s="145"/>
+      <c r="C134" s="144"/>
+      <c r="D134" s="144"/>
+      <c r="E134" s="144"/>
+      <c r="F134" s="144"/>
     </row>
     <row r="135" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C135" s="145"/>
-      <c r="D135" s="145"/>
-      <c r="E135" s="145"/>
-      <c r="F135" s="145"/>
+      <c r="C135" s="144"/>
+      <c r="D135" s="144"/>
+      <c r="E135" s="144"/>
+      <c r="F135" s="144"/>
     </row>
     <row r="136" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C136" s="145"/>
-      <c r="D136" s="145"/>
-      <c r="E136" s="145"/>
-      <c r="F136" s="145"/>
+      <c r="C136" s="144"/>
+      <c r="D136" s="144"/>
+      <c r="E136" s="144"/>
+      <c r="F136" s="144"/>
     </row>
     <row r="137" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C137" s="145"/>
-      <c r="D137" s="145"/>
-      <c r="E137" s="145"/>
-      <c r="F137" s="145"/>
+      <c r="C137" s="144"/>
+      <c r="D137" s="144"/>
+      <c r="E137" s="144"/>
+      <c r="F137" s="144"/>
     </row>
     <row r="138" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C138" s="145"/>
-      <c r="D138" s="145"/>
-      <c r="E138" s="145"/>
-      <c r="F138" s="145"/>
+      <c r="C138" s="144"/>
+      <c r="D138" s="144"/>
+      <c r="E138" s="144"/>
+      <c r="F138" s="144"/>
     </row>
     <row r="139" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C139" s="145"/>
-      <c r="D139" s="145"/>
-      <c r="E139" s="145"/>
-      <c r="F139" s="145"/>
+      <c r="C139" s="144"/>
+      <c r="D139" s="144"/>
+      <c r="E139" s="144"/>
+      <c r="F139" s="144"/>
     </row>
     <row r="140" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C140" s="145"/>
-      <c r="D140" s="145"/>
-      <c r="E140" s="145"/>
-      <c r="F140" s="145"/>
+      <c r="C140" s="144"/>
+      <c r="D140" s="144"/>
+      <c r="E140" s="144"/>
+      <c r="F140" s="144"/>
     </row>
     <row r="141" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C141" s="145"/>
-      <c r="D141" s="145"/>
-      <c r="E141" s="145"/>
-      <c r="F141" s="145"/>
+      <c r="C141" s="144"/>
+      <c r="D141" s="144"/>
+      <c r="E141" s="144"/>
+      <c r="F141" s="144"/>
     </row>
     <row r="142" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C142" s="145"/>
-      <c r="D142" s="145"/>
-      <c r="E142" s="145"/>
-      <c r="F142" s="145"/>
+      <c r="C142" s="144"/>
+      <c r="D142" s="144"/>
+      <c r="E142" s="144"/>
+      <c r="F142" s="144"/>
     </row>
     <row r="143" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C143" s="145"/>
-      <c r="D143" s="145"/>
-      <c r="E143" s="145"/>
-      <c r="F143" s="145"/>
+      <c r="C143" s="144"/>
+      <c r="D143" s="144"/>
+      <c r="E143" s="144"/>
+      <c r="F143" s="144"/>
     </row>
     <row r="144" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C144" s="145"/>
-      <c r="D144" s="145"/>
-      <c r="E144" s="145"/>
-      <c r="F144" s="145"/>
+      <c r="C144" s="144"/>
+      <c r="D144" s="144"/>
+      <c r="E144" s="144"/>
+      <c r="F144" s="144"/>
     </row>
     <row r="145" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C145" s="145"/>
-      <c r="D145" s="145"/>
-      <c r="E145" s="145"/>
-      <c r="F145" s="145"/>
+      <c r="C145" s="144"/>
+      <c r="D145" s="144"/>
+      <c r="E145" s="144"/>
+      <c r="F145" s="144"/>
     </row>
     <row r="146" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C146" s="145"/>
-      <c r="D146" s="145"/>
-      <c r="E146" s="145"/>
-      <c r="F146" s="145"/>
+      <c r="C146" s="144"/>
+      <c r="D146" s="144"/>
+      <c r="E146" s="144"/>
+      <c r="F146" s="144"/>
     </row>
     <row r="147" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C147" s="145"/>
-      <c r="D147" s="145"/>
-      <c r="E147" s="145"/>
-      <c r="F147" s="145"/>
+      <c r="C147" s="144"/>
+      <c r="D147" s="144"/>
+      <c r="E147" s="144"/>
+      <c r="F147" s="144"/>
     </row>
     <row r="148" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C148" s="145"/>
-      <c r="D148" s="145"/>
-      <c r="E148" s="145"/>
-      <c r="F148" s="145"/>
+      <c r="C148" s="144"/>
+      <c r="D148" s="144"/>
+      <c r="E148" s="144"/>
+      <c r="F148" s="144"/>
     </row>
     <row r="149" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C149" s="145"/>
-      <c r="D149" s="145"/>
-      <c r="E149" s="145"/>
-      <c r="F149" s="145"/>
+      <c r="C149" s="144"/>
+      <c r="D149" s="144"/>
+      <c r="E149" s="144"/>
+      <c r="F149" s="144"/>
     </row>
     <row r="150" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C150" s="145"/>
-      <c r="D150" s="145"/>
-      <c r="E150" s="145"/>
-      <c r="F150" s="145"/>
+      <c r="C150" s="144"/>
+      <c r="D150" s="144"/>
+      <c r="E150" s="144"/>
+      <c r="F150" s="144"/>
     </row>
     <row r="151" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C151" s="145"/>
-      <c r="D151" s="145"/>
-      <c r="E151" s="145"/>
-      <c r="F151" s="145"/>
+      <c r="C151" s="144"/>
+      <c r="D151" s="144"/>
+      <c r="E151" s="144"/>
+      <c r="F151" s="144"/>
     </row>
     <row r="152" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C152" s="145"/>
-      <c r="D152" s="145"/>
-      <c r="E152" s="145"/>
-      <c r="F152" s="145"/>
+      <c r="C152" s="144"/>
+      <c r="D152" s="144"/>
+      <c r="E152" s="144"/>
+      <c r="F152" s="144"/>
     </row>
     <row r="153" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C153" s="145"/>
-      <c r="D153" s="145"/>
-      <c r="E153" s="145"/>
-      <c r="F153" s="145"/>
+      <c r="C153" s="144"/>
+      <c r="D153" s="144"/>
+      <c r="E153" s="144"/>
+      <c r="F153" s="144"/>
     </row>
     <row r="154" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C154" s="145"/>
-      <c r="D154" s="145"/>
-      <c r="E154" s="145"/>
-      <c r="F154" s="145"/>
+      <c r="C154" s="144"/>
+      <c r="D154" s="144"/>
+      <c r="E154" s="144"/>
+      <c r="F154" s="144"/>
     </row>
     <row r="155" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C155" s="145"/>
-      <c r="D155" s="145"/>
-      <c r="E155" s="145"/>
-      <c r="F155" s="145"/>
+      <c r="C155" s="144"/>
+      <c r="D155" s="144"/>
+      <c r="E155" s="144"/>
+      <c r="F155" s="144"/>
     </row>
     <row r="156" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C156" s="145"/>
-      <c r="D156" s="145"/>
-      <c r="E156" s="145"/>
-      <c r="F156" s="145"/>
+      <c r="C156" s="144"/>
+      <c r="D156" s="144"/>
+      <c r="E156" s="144"/>
+      <c r="F156" s="144"/>
     </row>
     <row r="157" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C157" s="145"/>
-      <c r="D157" s="145"/>
-      <c r="E157" s="145"/>
-      <c r="F157" s="145"/>
+      <c r="C157" s="144"/>
+      <c r="D157" s="144"/>
+      <c r="E157" s="144"/>
+      <c r="F157" s="144"/>
     </row>
     <row r="158" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C158" s="145"/>
-      <c r="D158" s="145"/>
-      <c r="E158" s="145"/>
-      <c r="F158" s="145"/>
+      <c r="C158" s="144"/>
+      <c r="D158" s="144"/>
+      <c r="E158" s="144"/>
+      <c r="F158" s="144"/>
     </row>
     <row r="159" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C159" s="145"/>
-      <c r="D159" s="145"/>
-      <c r="E159" s="145"/>
-      <c r="F159" s="145"/>
+      <c r="C159" s="144"/>
+      <c r="D159" s="144"/>
+      <c r="E159" s="144"/>
+      <c r="F159" s="144"/>
     </row>
     <row r="160" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C160" s="145"/>
-      <c r="D160" s="145"/>
-      <c r="E160" s="145"/>
-      <c r="F160" s="145"/>
+      <c r="C160" s="144"/>
+      <c r="D160" s="144"/>
+      <c r="E160" s="144"/>
+      <c r="F160" s="144"/>
     </row>
     <row r="161" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C161" s="145"/>
-      <c r="D161" s="145"/>
-      <c r="E161" s="145"/>
-      <c r="F161" s="145"/>
+      <c r="C161" s="144"/>
+      <c r="D161" s="144"/>
+      <c r="E161" s="144"/>
+      <c r="F161" s="144"/>
     </row>
     <row r="162" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C162" s="145"/>
-      <c r="D162" s="145"/>
-      <c r="E162" s="145"/>
-      <c r="F162" s="145"/>
+      <c r="C162" s="144"/>
+      <c r="D162" s="144"/>
+      <c r="E162" s="144"/>
+      <c r="F162" s="144"/>
     </row>
     <row r="163" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C163" s="145"/>
-      <c r="D163" s="145"/>
-      <c r="E163" s="145"/>
-      <c r="F163" s="145"/>
+      <c r="C163" s="144"/>
+      <c r="D163" s="144"/>
+      <c r="E163" s="144"/>
+      <c r="F163" s="144"/>
     </row>
     <row r="164" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C164" s="145"/>
-      <c r="D164" s="145"/>
-      <c r="E164" s="145"/>
-      <c r="F164" s="145"/>
+      <c r="C164" s="144"/>
+      <c r="D164" s="144"/>
+      <c r="E164" s="144"/>
+      <c r="F164" s="144"/>
     </row>
     <row r="165" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C165" s="145"/>
-      <c r="D165" s="145"/>
-      <c r="E165" s="145"/>
-      <c r="F165" s="145"/>
+      <c r="C165" s="144"/>
+      <c r="D165" s="144"/>
+      <c r="E165" s="144"/>
+      <c r="F165" s="144"/>
     </row>
     <row r="166" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C166" s="145"/>
-      <c r="D166" s="145"/>
-      <c r="E166" s="145"/>
-      <c r="F166" s="145"/>
+      <c r="C166" s="144"/>
+      <c r="D166" s="144"/>
+      <c r="E166" s="144"/>
+      <c r="F166" s="144"/>
     </row>
     <row r="167" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C167" s="145"/>
-      <c r="D167" s="145"/>
-      <c r="E167" s="145"/>
-      <c r="F167" s="145"/>
+      <c r="C167" s="144"/>
+      <c r="D167" s="144"/>
+      <c r="E167" s="144"/>
+      <c r="F167" s="144"/>
     </row>
     <row r="168" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C168" s="145"/>
-      <c r="D168" s="145"/>
-      <c r="E168" s="145"/>
-      <c r="F168" s="145"/>
+      <c r="C168" s="144"/>
+      <c r="D168" s="144"/>
+      <c r="E168" s="144"/>
+      <c r="F168" s="144"/>
     </row>
     <row r="169" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C169" s="145"/>
-      <c r="D169" s="145"/>
-      <c r="E169" s="145"/>
-      <c r="F169" s="145"/>
+      <c r="C169" s="144"/>
+      <c r="D169" s="144"/>
+      <c r="E169" s="144"/>
+      <c r="F169" s="144"/>
     </row>
     <row r="170" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C170" s="145"/>
-      <c r="D170" s="145"/>
-      <c r="E170" s="145"/>
-      <c r="F170" s="145"/>
+      <c r="C170" s="144"/>
+      <c r="D170" s="144"/>
+      <c r="E170" s="144"/>
+      <c r="F170" s="144"/>
     </row>
     <row r="171" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C171" s="145"/>
-      <c r="D171" s="145"/>
-      <c r="E171" s="145"/>
-      <c r="F171" s="145"/>
+      <c r="C171" s="144"/>
+      <c r="D171" s="144"/>
+      <c r="E171" s="144"/>
+      <c r="F171" s="144"/>
     </row>
     <row r="172" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C172" s="145"/>
-      <c r="D172" s="145"/>
-      <c r="E172" s="145"/>
-      <c r="F172" s="145"/>
+      <c r="C172" s="144"/>
+      <c r="D172" s="144"/>
+      <c r="E172" s="144"/>
+      <c r="F172" s="144"/>
     </row>
     <row r="173" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C173" s="145"/>
-      <c r="D173" s="145"/>
-      <c r="E173" s="145"/>
-      <c r="F173" s="145"/>
+      <c r="C173" s="144"/>
+      <c r="D173" s="144"/>
+      <c r="E173" s="144"/>
+      <c r="F173" s="144"/>
     </row>
     <row r="174" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C174" s="145"/>
-      <c r="D174" s="145"/>
-      <c r="E174" s="145"/>
-      <c r="F174" s="145"/>
+      <c r="C174" s="144"/>
+      <c r="D174" s="144"/>
+      <c r="E174" s="144"/>
+      <c r="F174" s="144"/>
     </row>
     <row r="175" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C175" s="145"/>
-      <c r="D175" s="145"/>
-      <c r="E175" s="145"/>
-      <c r="F175" s="145"/>
+      <c r="C175" s="144"/>
+      <c r="D175" s="144"/>
+      <c r="E175" s="144"/>
+      <c r="F175" s="144"/>
     </row>
     <row r="176" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C176" s="145"/>
-      <c r="D176" s="145"/>
-      <c r="E176" s="145"/>
-      <c r="F176" s="145"/>
+      <c r="C176" s="144"/>
+      <c r="D176" s="144"/>
+      <c r="E176" s="144"/>
+      <c r="F176" s="144"/>
     </row>
     <row r="177" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C177" s="145"/>
-      <c r="D177" s="145"/>
-      <c r="E177" s="145"/>
-      <c r="F177" s="145"/>
+      <c r="C177" s="144"/>
+      <c r="D177" s="144"/>
+      <c r="E177" s="144"/>
+      <c r="F177" s="144"/>
     </row>
     <row r="178" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C178" s="145"/>
-      <c r="D178" s="145"/>
-      <c r="E178" s="145"/>
-      <c r="F178" s="145"/>
+      <c r="C178" s="144"/>
+      <c r="D178" s="144"/>
+      <c r="E178" s="144"/>
+      <c r="F178" s="144"/>
     </row>
     <row r="179" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C179" s="145"/>
-      <c r="D179" s="145"/>
-      <c r="E179" s="145"/>
-      <c r="F179" s="145"/>
+      <c r="C179" s="144"/>
+      <c r="D179" s="144"/>
+      <c r="E179" s="144"/>
+      <c r="F179" s="144"/>
     </row>
     <row r="180" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C180" s="145"/>
-      <c r="D180" s="145"/>
-      <c r="E180" s="145"/>
-      <c r="F180" s="145"/>
+      <c r="C180" s="144"/>
+      <c r="D180" s="144"/>
+      <c r="E180" s="144"/>
+      <c r="F180" s="144"/>
     </row>
     <row r="181" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C181" s="145"/>
-      <c r="D181" s="145"/>
-      <c r="E181" s="145"/>
-      <c r="F181" s="145"/>
+      <c r="C181" s="144"/>
+      <c r="D181" s="144"/>
+      <c r="E181" s="144"/>
+      <c r="F181" s="144"/>
     </row>
     <row r="182" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C182" s="145"/>
-      <c r="D182" s="145"/>
-      <c r="E182" s="145"/>
-      <c r="F182" s="145"/>
+      <c r="C182" s="144"/>
+      <c r="D182" s="144"/>
+      <c r="E182" s="144"/>
+      <c r="F182" s="144"/>
     </row>
     <row r="183" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C183" s="145"/>
-      <c r="D183" s="145"/>
-      <c r="E183" s="145"/>
-      <c r="F183" s="145"/>
+      <c r="C183" s="144"/>
+      <c r="D183" s="144"/>
+      <c r="E183" s="144"/>
+      <c r="F183" s="144"/>
     </row>
     <row r="184" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C184" s="145"/>
-      <c r="D184" s="145"/>
-      <c r="E184" s="145"/>
-      <c r="F184" s="145"/>
+      <c r="C184" s="144"/>
+      <c r="D184" s="144"/>
+      <c r="E184" s="144"/>
+      <c r="F184" s="144"/>
     </row>
     <row r="185" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C185" s="145"/>
-      <c r="D185" s="145"/>
-      <c r="E185" s="145"/>
-      <c r="F185" s="145"/>
+      <c r="C185" s="144"/>
+      <c r="D185" s="144"/>
+      <c r="E185" s="144"/>
+      <c r="F185" s="144"/>
     </row>
     <row r="186" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C186" s="145"/>
-      <c r="D186" s="145"/>
-      <c r="E186" s="145"/>
-      <c r="F186" s="145"/>
+      <c r="C186" s="144"/>
+      <c r="D186" s="144"/>
+      <c r="E186" s="144"/>
+      <c r="F186" s="144"/>
     </row>
     <row r="187" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C187" s="145"/>
-      <c r="D187" s="145"/>
-      <c r="E187" s="145"/>
-      <c r="F187" s="145"/>
+      <c r="C187" s="144"/>
+      <c r="D187" s="144"/>
+      <c r="E187" s="144"/>
+      <c r="F187" s="144"/>
     </row>
     <row r="188" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C188" s="145"/>
-      <c r="D188" s="145"/>
-      <c r="E188" s="145"/>
-      <c r="F188" s="145"/>
+      <c r="C188" s="144"/>
+      <c r="D188" s="144"/>
+      <c r="E188" s="144"/>
+      <c r="F188" s="144"/>
     </row>
     <row r="189" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C189" s="145"/>
-      <c r="D189" s="145"/>
-      <c r="E189" s="145"/>
-      <c r="F189" s="145"/>
+      <c r="C189" s="144"/>
+      <c r="D189" s="144"/>
+      <c r="E189" s="144"/>
+      <c r="F189" s="144"/>
     </row>
     <row r="190" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C190" s="145"/>
-      <c r="D190" s="145"/>
-      <c r="E190" s="145"/>
-      <c r="F190" s="145"/>
+      <c r="C190" s="144"/>
+      <c r="D190" s="144"/>
+      <c r="E190" s="144"/>
+      <c r="F190" s="144"/>
     </row>
     <row r="191" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C191" s="145"/>
-      <c r="D191" s="145"/>
-      <c r="E191" s="145"/>
-      <c r="F191" s="145"/>
+      <c r="C191" s="144"/>
+      <c r="D191" s="144"/>
+      <c r="E191" s="144"/>
+      <c r="F191" s="144"/>
     </row>
     <row r="192" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C192" s="145"/>
-      <c r="D192" s="145"/>
-      <c r="E192" s="145"/>
-      <c r="F192" s="145"/>
+      <c r="C192" s="144"/>
+      <c r="D192" s="144"/>
+      <c r="E192" s="144"/>
+      <c r="F192" s="144"/>
     </row>
     <row r="193" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C193" s="145"/>
-      <c r="D193" s="145"/>
-      <c r="E193" s="145"/>
-      <c r="F193" s="145"/>
+      <c r="C193" s="144"/>
+      <c r="D193" s="144"/>
+      <c r="E193" s="144"/>
+      <c r="F193" s="144"/>
     </row>
     <row r="194" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C194" s="145"/>
-      <c r="D194" s="145"/>
-      <c r="E194" s="145"/>
-      <c r="F194" s="145"/>
+      <c r="C194" s="144"/>
+      <c r="D194" s="144"/>
+      <c r="E194" s="144"/>
+      <c r="F194" s="144"/>
     </row>
     <row r="195" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C195" s="145"/>
-      <c r="D195" s="145"/>
-      <c r="E195" s="145"/>
-      <c r="F195" s="145"/>
+      <c r="C195" s="144"/>
+      <c r="D195" s="144"/>
+      <c r="E195" s="144"/>
+      <c r="F195" s="144"/>
     </row>
     <row r="196" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C196" s="145"/>
-      <c r="D196" s="145"/>
-      <c r="E196" s="145"/>
-      <c r="F196" s="145"/>
+      <c r="C196" s="144"/>
+      <c r="D196" s="144"/>
+      <c r="E196" s="144"/>
+      <c r="F196" s="144"/>
     </row>
     <row r="197" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C197" s="145"/>
-      <c r="D197" s="145"/>
-      <c r="E197" s="145"/>
-      <c r="F197" s="145"/>
+      <c r="C197" s="144"/>
+      <c r="D197" s="144"/>
+      <c r="E197" s="144"/>
+      <c r="F197" s="144"/>
     </row>
     <row r="198" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C198" s="145"/>
-      <c r="D198" s="145"/>
-      <c r="E198" s="145"/>
-      <c r="F198" s="145"/>
+      <c r="C198" s="144"/>
+      <c r="D198" s="144"/>
+      <c r="E198" s="144"/>
+      <c r="F198" s="144"/>
     </row>
     <row r="199" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C199" s="145"/>
-      <c r="D199" s="145"/>
-      <c r="E199" s="145"/>
-      <c r="F199" s="145"/>
+      <c r="C199" s="144"/>
+      <c r="D199" s="144"/>
+      <c r="E199" s="144"/>
+      <c r="F199" s="144"/>
     </row>
     <row r="200" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C200" s="145"/>
-      <c r="D200" s="145"/>
-      <c r="E200" s="145"/>
-      <c r="F200" s="145"/>
+      <c r="C200" s="144"/>
+      <c r="D200" s="144"/>
+      <c r="E200" s="144"/>
+      <c r="F200" s="144"/>
     </row>
     <row r="201" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C201" s="145"/>
-      <c r="D201" s="145"/>
-      <c r="E201" s="145"/>
-      <c r="F201" s="145"/>
+      <c r="C201" s="144"/>
+      <c r="D201" s="144"/>
+      <c r="E201" s="144"/>
+      <c r="F201" s="144"/>
     </row>
     <row r="202" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C202" s="145"/>
-      <c r="D202" s="145"/>
-      <c r="E202" s="145"/>
-      <c r="F202" s="145"/>
+      <c r="C202" s="144"/>
+      <c r="D202" s="144"/>
+      <c r="E202" s="144"/>
+      <c r="F202" s="144"/>
     </row>
     <row r="203" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C203" s="145"/>
-      <c r="D203" s="145"/>
-      <c r="E203" s="145"/>
-      <c r="F203" s="145"/>
+      <c r="C203" s="144"/>
+      <c r="D203" s="144"/>
+      <c r="E203" s="144"/>
+      <c r="F203" s="144"/>
     </row>
     <row r="204" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C204" s="145"/>
-      <c r="D204" s="145"/>
-      <c r="E204" s="145"/>
-      <c r="F204" s="145"/>
+      <c r="C204" s="144"/>
+      <c r="D204" s="144"/>
+      <c r="E204" s="144"/>
+      <c r="F204" s="144"/>
     </row>
     <row r="205" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C205" s="145"/>
-      <c r="D205" s="145"/>
-      <c r="E205" s="145"/>
-      <c r="F205" s="145"/>
+      <c r="C205" s="144"/>
+      <c r="D205" s="144"/>
+      <c r="E205" s="144"/>
+      <c r="F205" s="144"/>
     </row>
     <row r="206" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C206" s="145"/>
-      <c r="D206" s="145"/>
-      <c r="E206" s="145"/>
-      <c r="F206" s="145"/>
+      <c r="C206" s="144"/>
+      <c r="D206" s="144"/>
+      <c r="E206" s="144"/>
+      <c r="F206" s="144"/>
     </row>
     <row r="207" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C207" s="145"/>
-      <c r="D207" s="145"/>
-      <c r="E207" s="145"/>
-      <c r="F207" s="145"/>
+      <c r="C207" s="144"/>
+      <c r="D207" s="144"/>
+      <c r="E207" s="144"/>
+      <c r="F207" s="144"/>
     </row>
     <row r="208" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C208" s="145"/>
-      <c r="D208" s="145"/>
-      <c r="E208" s="145"/>
-      <c r="F208" s="145"/>
+      <c r="C208" s="144"/>
+      <c r="D208" s="144"/>
+      <c r="E208" s="144"/>
+      <c r="F208" s="144"/>
     </row>
     <row r="209" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C209" s="145"/>
-      <c r="D209" s="145"/>
-      <c r="E209" s="145"/>
-      <c r="F209" s="145"/>
+      <c r="C209" s="144"/>
+      <c r="D209" s="144"/>
+      <c r="E209" s="144"/>
+      <c r="F209" s="144"/>
     </row>
     <row r="210" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C210" s="145"/>
-      <c r="D210" s="145"/>
-      <c r="E210" s="145"/>
-      <c r="F210" s="145"/>
+      <c r="C210" s="144"/>
+      <c r="D210" s="144"/>
+      <c r="E210" s="144"/>
+      <c r="F210" s="144"/>
     </row>
     <row r="211" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C211" s="145"/>
-      <c r="D211" s="145"/>
-      <c r="E211" s="145"/>
-      <c r="F211" s="145"/>
+      <c r="C211" s="144"/>
+      <c r="D211" s="144"/>
+      <c r="E211" s="144"/>
+      <c r="F211" s="144"/>
     </row>
     <row r="212" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C212" s="145"/>
-      <c r="D212" s="145"/>
-      <c r="E212" s="145"/>
-      <c r="F212" s="145"/>
+      <c r="C212" s="144"/>
+      <c r="D212" s="144"/>
+      <c r="E212" s="144"/>
+      <c r="F212" s="144"/>
     </row>
     <row r="213" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C213" s="145"/>
-      <c r="D213" s="145"/>
-      <c r="E213" s="145"/>
-      <c r="F213" s="145"/>
+      <c r="C213" s="144"/>
+      <c r="D213" s="144"/>
+      <c r="E213" s="144"/>
+      <c r="F213" s="144"/>
     </row>
     <row r="214" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C214" s="145"/>
-      <c r="D214" s="145"/>
-      <c r="E214" s="145"/>
-      <c r="F214" s="145"/>
+      <c r="C214" s="144"/>
+      <c r="D214" s="144"/>
+      <c r="E214" s="144"/>
+      <c r="F214" s="144"/>
     </row>
     <row r="215" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C215" s="145"/>
-      <c r="D215" s="145"/>
-      <c r="E215" s="145"/>
-      <c r="F215" s="145"/>
+      <c r="C215" s="144"/>
+      <c r="D215" s="144"/>
+      <c r="E215" s="144"/>
+      <c r="F215" s="144"/>
     </row>
     <row r="216" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C216" s="145"/>
-      <c r="D216" s="145"/>
-      <c r="E216" s="145"/>
-      <c r="F216" s="145"/>
+      <c r="C216" s="144"/>
+      <c r="D216" s="144"/>
+      <c r="E216" s="144"/>
+      <c r="F216" s="144"/>
     </row>
     <row r="217" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C217" s="145"/>
-      <c r="D217" s="145"/>
-      <c r="E217" s="145"/>
-      <c r="F217" s="145"/>
+      <c r="C217" s="144"/>
+      <c r="D217" s="144"/>
+      <c r="E217" s="144"/>
+      <c r="F217" s="144"/>
     </row>
     <row r="218" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C218" s="145"/>
-      <c r="D218" s="145"/>
-      <c r="E218" s="145"/>
-      <c r="F218" s="145"/>
+      <c r="C218" s="144"/>
+      <c r="D218" s="144"/>
+      <c r="E218" s="144"/>
+      <c r="F218" s="144"/>
     </row>
     <row r="219" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C219" s="145"/>
-      <c r="D219" s="145"/>
-      <c r="E219" s="145"/>
-      <c r="F219" s="145"/>
+      <c r="C219" s="144"/>
+      <c r="D219" s="144"/>
+      <c r="E219" s="144"/>
+      <c r="F219" s="144"/>
     </row>
     <row r="220" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C220" s="145"/>
-      <c r="D220" s="145"/>
-      <c r="E220" s="145"/>
-      <c r="F220" s="145"/>
+      <c r="C220" s="144"/>
+      <c r="D220" s="144"/>
+      <c r="E220" s="144"/>
+      <c r="F220" s="144"/>
     </row>
     <row r="221" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C221" s="145"/>
-      <c r="D221" s="145"/>
-      <c r="E221" s="145"/>
-      <c r="F221" s="145"/>
+      <c r="C221" s="144"/>
+      <c r="D221" s="144"/>
+      <c r="E221" s="144"/>
+      <c r="F221" s="144"/>
     </row>
     <row r="222" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C222" s="145"/>
-      <c r="D222" s="145"/>
-      <c r="E222" s="145"/>
-      <c r="F222" s="145"/>
+      <c r="C222" s="144"/>
+      <c r="D222" s="144"/>
+      <c r="E222" s="144"/>
+      <c r="F222" s="144"/>
     </row>
     <row r="223" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C223" s="145"/>
-      <c r="D223" s="145"/>
-      <c r="E223" s="145"/>
-      <c r="F223" s="145"/>
+      <c r="C223" s="144"/>
+      <c r="D223" s="144"/>
+      <c r="E223" s="144"/>
+      <c r="F223" s="144"/>
     </row>
     <row r="224" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C224" s="145"/>
-      <c r="D224" s="145"/>
-      <c r="E224" s="145"/>
-      <c r="F224" s="145"/>
+      <c r="C224" s="144"/>
+      <c r="D224" s="144"/>
+      <c r="E224" s="144"/>
+      <c r="F224" s="144"/>
     </row>
     <row r="225" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C225" s="145"/>
-      <c r="D225" s="145"/>
-      <c r="E225" s="145"/>
-      <c r="F225" s="145"/>
+      <c r="C225" s="144"/>
+      <c r="D225" s="144"/>
+      <c r="E225" s="144"/>
+      <c r="F225" s="144"/>
     </row>
     <row r="226" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C226" s="145"/>
-      <c r="D226" s="145"/>
-      <c r="E226" s="145"/>
-      <c r="F226" s="145"/>
+      <c r="C226" s="144"/>
+      <c r="D226" s="144"/>
+      <c r="E226" s="144"/>
+      <c r="F226" s="144"/>
     </row>
     <row r="227" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C227" s="145"/>
-      <c r="D227" s="145"/>
-      <c r="E227" s="145"/>
-      <c r="F227" s="145"/>
+      <c r="C227" s="144"/>
+      <c r="D227" s="144"/>
+      <c r="E227" s="144"/>
+      <c r="F227" s="144"/>
     </row>
     <row r="228" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C228" s="145"/>
-      <c r="D228" s="145"/>
-      <c r="E228" s="145"/>
-      <c r="F228" s="145"/>
+      <c r="C228" s="144"/>
+      <c r="D228" s="144"/>
+      <c r="E228" s="144"/>
+      <c r="F228" s="144"/>
     </row>
     <row r="229" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C229" s="145"/>
-      <c r="D229" s="145"/>
-      <c r="E229" s="145"/>
-      <c r="F229" s="145"/>
+      <c r="C229" s="144"/>
+      <c r="D229" s="144"/>
+      <c r="E229" s="144"/>
+      <c r="F229" s="144"/>
     </row>
     <row r="230" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C230" s="145"/>
-      <c r="D230" s="145"/>
-      <c r="E230" s="145"/>
-      <c r="F230" s="145"/>
+      <c r="C230" s="144"/>
+      <c r="D230" s="144"/>
+      <c r="E230" s="144"/>
+      <c r="F230" s="144"/>
     </row>
     <row r="231" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C231" s="145"/>
-      <c r="D231" s="145"/>
-      <c r="E231" s="145"/>
-      <c r="F231" s="145"/>
+      <c r="C231" s="144"/>
+      <c r="D231" s="144"/>
+      <c r="E231" s="144"/>
+      <c r="F231" s="144"/>
     </row>
     <row r="232" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C232" s="145"/>
-      <c r="D232" s="145"/>
-      <c r="E232" s="145"/>
-      <c r="F232" s="145"/>
+      <c r="C232" s="144"/>
+      <c r="D232" s="144"/>
+      <c r="E232" s="144"/>
+      <c r="F232" s="144"/>
     </row>
     <row r="233" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C233" s="145"/>
-      <c r="D233" s="145"/>
-      <c r="E233" s="145"/>
-      <c r="F233" s="145"/>
+      <c r="C233" s="144"/>
+      <c r="D233" s="144"/>
+      <c r="E233" s="144"/>
+      <c r="F233" s="144"/>
     </row>
     <row r="234" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C234" s="145"/>
-      <c r="D234" s="145"/>
-      <c r="E234" s="145"/>
-      <c r="F234" s="145"/>
+      <c r="C234" s="144"/>
+      <c r="D234" s="144"/>
+      <c r="E234" s="144"/>
+      <c r="F234" s="144"/>
     </row>
     <row r="235" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C235" s="145"/>
-      <c r="D235" s="145"/>
-      <c r="E235" s="145"/>
-      <c r="F235" s="145"/>
+      <c r="C235" s="144"/>
+      <c r="D235" s="144"/>
+      <c r="E235" s="144"/>
+      <c r="F235" s="144"/>
     </row>
     <row r="236" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C236" s="145"/>
-      <c r="D236" s="145"/>
-      <c r="E236" s="145"/>
-      <c r="F236" s="145"/>
+      <c r="C236" s="144"/>
+      <c r="D236" s="144"/>
+      <c r="E236" s="144"/>
+      <c r="F236" s="144"/>
     </row>
     <row r="237" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C237" s="145"/>
-      <c r="D237" s="145"/>
-      <c r="E237" s="145"/>
-      <c r="F237" s="145"/>
+      <c r="C237" s="144"/>
+      <c r="D237" s="144"/>
+      <c r="E237" s="144"/>
+      <c r="F237" s="144"/>
     </row>
     <row r="238" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C238" s="145"/>
-      <c r="D238" s="145"/>
-      <c r="E238" s="145"/>
-      <c r="F238" s="145"/>
+      <c r="C238" s="144"/>
+      <c r="D238" s="144"/>
+      <c r="E238" s="144"/>
+      <c r="F238" s="144"/>
     </row>
     <row r="239" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C239" s="145"/>
-      <c r="D239" s="145"/>
-      <c r="E239" s="145"/>
-      <c r="F239" s="145"/>
+      <c r="C239" s="144"/>
+      <c r="D239" s="144"/>
+      <c r="E239" s="144"/>
+      <c r="F239" s="144"/>
     </row>
     <row r="240" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C240" s="145"/>
-      <c r="D240" s="145"/>
-      <c r="E240" s="145"/>
-      <c r="F240" s="145"/>
+      <c r="C240" s="144"/>
+      <c r="D240" s="144"/>
+      <c r="E240" s="144"/>
+      <c r="F240" s="144"/>
     </row>
     <row r="241" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C241" s="145"/>
-      <c r="D241" s="145"/>
-      <c r="E241" s="145"/>
-      <c r="F241" s="145"/>
+      <c r="C241" s="144"/>
+      <c r="D241" s="144"/>
+      <c r="E241" s="144"/>
+      <c r="F241" s="144"/>
     </row>
     <row r="242" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C242" s="145"/>
-      <c r="D242" s="145"/>
-      <c r="E242" s="145"/>
-      <c r="F242" s="145"/>
+      <c r="C242" s="144"/>
+      <c r="D242" s="144"/>
+      <c r="E242" s="144"/>
+      <c r="F242" s="144"/>
     </row>
     <row r="243" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C243" s="145"/>
-      <c r="D243" s="145"/>
-      <c r="E243" s="145"/>
-      <c r="F243" s="145"/>
+      <c r="C243" s="144"/>
+      <c r="D243" s="144"/>
+      <c r="E243" s="144"/>
+      <c r="F243" s="144"/>
     </row>
     <row r="244" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C244" s="145"/>
-      <c r="D244" s="145"/>
-      <c r="E244" s="145"/>
-      <c r="F244" s="145"/>
+      <c r="C244" s="144"/>
+      <c r="D244" s="144"/>
+      <c r="E244" s="144"/>
+      <c r="F244" s="144"/>
     </row>
     <row r="245" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C245" s="145"/>
-      <c r="D245" s="145"/>
-      <c r="E245" s="145"/>
-      <c r="F245" s="145"/>
+      <c r="C245" s="144"/>
+      <c r="D245" s="144"/>
+      <c r="E245" s="144"/>
+      <c r="F245" s="144"/>
     </row>
     <row r="246" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C246" s="145"/>
-      <c r="D246" s="145"/>
-      <c r="E246" s="145"/>
-      <c r="F246" s="145"/>
+      <c r="C246" s="144"/>
+      <c r="D246" s="144"/>
+      <c r="E246" s="144"/>
+      <c r="F246" s="144"/>
     </row>
     <row r="247" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C247" s="145"/>
-      <c r="D247" s="145"/>
-      <c r="E247" s="145"/>
-      <c r="F247" s="145"/>
+      <c r="C247" s="144"/>
+      <c r="D247" s="144"/>
+      <c r="E247" s="144"/>
+      <c r="F247" s="144"/>
     </row>
     <row r="248" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C248" s="145"/>
-      <c r="D248" s="145"/>
-      <c r="E248" s="145"/>
-      <c r="F248" s="145"/>
+      <c r="C248" s="144"/>
+      <c r="D248" s="144"/>
+      <c r="E248" s="144"/>
+      <c r="F248" s="144"/>
     </row>
     <row r="249" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C249" s="145"/>
-      <c r="D249" s="145"/>
-      <c r="E249" s="145"/>
-      <c r="F249" s="145"/>
+      <c r="C249" s="144"/>
+      <c r="D249" s="144"/>
+      <c r="E249" s="144"/>
+      <c r="F249" s="144"/>
     </row>
     <row r="250" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C250" s="145"/>
-      <c r="D250" s="145"/>
-      <c r="E250" s="145"/>
-      <c r="F250" s="145"/>
+      <c r="C250" s="144"/>
+      <c r="D250" s="144"/>
+      <c r="E250" s="144"/>
+      <c r="F250" s="144"/>
     </row>
     <row r="251" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C251" s="145"/>
-      <c r="D251" s="145"/>
-      <c r="E251" s="145"/>
-      <c r="F251" s="145"/>
+      <c r="C251" s="144"/>
+      <c r="D251" s="144"/>
+      <c r="E251" s="144"/>
+      <c r="F251" s="144"/>
     </row>
     <row r="252" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C252" s="145"/>
-      <c r="D252" s="145"/>
-      <c r="E252" s="145"/>
-      <c r="F252" s="145"/>
+      <c r="C252" s="144"/>
+      <c r="D252" s="144"/>
+      <c r="E252" s="144"/>
+      <c r="F252" s="144"/>
     </row>
     <row r="253" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C253" s="145"/>
-      <c r="D253" s="145"/>
-      <c r="E253" s="145"/>
-      <c r="F253" s="145"/>
+      <c r="C253" s="144"/>
+      <c r="D253" s="144"/>
+      <c r="E253" s="144"/>
+      <c r="F253" s="144"/>
     </row>
     <row r="254" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C254" s="145"/>
-      <c r="D254" s="145"/>
-      <c r="E254" s="145"/>
-      <c r="F254" s="145"/>
+      <c r="C254" s="144"/>
+      <c r="D254" s="144"/>
+      <c r="E254" s="144"/>
+      <c r="F254" s="144"/>
     </row>
     <row r="255" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C255" s="145"/>
-      <c r="D255" s="145"/>
-      <c r="E255" s="145"/>
-      <c r="F255" s="145"/>
+      <c r="C255" s="144"/>
+      <c r="D255" s="144"/>
+      <c r="E255" s="144"/>
+      <c r="F255" s="144"/>
     </row>
     <row r="256" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C256" s="145"/>
-      <c r="D256" s="145"/>
-      <c r="E256" s="145"/>
-      <c r="F256" s="145"/>
+      <c r="C256" s="144"/>
+      <c r="D256" s="144"/>
+      <c r="E256" s="144"/>
+      <c r="F256" s="144"/>
     </row>
     <row r="257" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C257" s="145"/>
-      <c r="D257" s="145"/>
-      <c r="E257" s="145"/>
-      <c r="F257" s="145"/>
+      <c r="C257" s="144"/>
+      <c r="D257" s="144"/>
+      <c r="E257" s="144"/>
+      <c r="F257" s="144"/>
     </row>
     <row r="258" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C258" s="145"/>
-      <c r="D258" s="145"/>
-      <c r="E258" s="145"/>
-      <c r="F258" s="145"/>
+      <c r="C258" s="144"/>
+      <c r="D258" s="144"/>
+      <c r="E258" s="144"/>
+      <c r="F258" s="144"/>
     </row>
     <row r="259" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C259" s="145"/>
-      <c r="D259" s="145"/>
-      <c r="E259" s="145"/>
-      <c r="F259" s="145"/>
+      <c r="C259" s="144"/>
+      <c r="D259" s="144"/>
+      <c r="E259" s="144"/>
+      <c r="F259" s="144"/>
     </row>
     <row r="260" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C260" s="145"/>
-      <c r="D260" s="145"/>
-      <c r="E260" s="145"/>
-      <c r="F260" s="145"/>
+      <c r="C260" s="144"/>
+      <c r="D260" s="144"/>
+      <c r="E260" s="144"/>
+      <c r="F260" s="144"/>
     </row>
     <row r="261" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C261" s="145"/>
-      <c r="D261" s="145"/>
-      <c r="E261" s="145"/>
-      <c r="F261" s="145"/>
+      <c r="C261" s="144"/>
+      <c r="D261" s="144"/>
+      <c r="E261" s="144"/>
+      <c r="F261" s="144"/>
     </row>
     <row r="262" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C262" s="145"/>
-      <c r="D262" s="145"/>
-      <c r="E262" s="145"/>
-      <c r="F262" s="145"/>
+      <c r="C262" s="144"/>
+      <c r="D262" s="144"/>
+      <c r="E262" s="144"/>
+      <c r="F262" s="144"/>
     </row>
     <row r="263" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C263" s="145"/>
-      <c r="D263" s="145"/>
-      <c r="E263" s="145"/>
-      <c r="F263" s="145"/>
+      <c r="C263" s="144"/>
+      <c r="D263" s="144"/>
+      <c r="E263" s="144"/>
+      <c r="F263" s="144"/>
     </row>
     <row r="264" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C264" s="145"/>
-      <c r="D264" s="145"/>
-      <c r="E264" s="145"/>
-      <c r="F264" s="145"/>
+      <c r="C264" s="144"/>
+      <c r="D264" s="144"/>
+      <c r="E264" s="144"/>
+      <c r="F264" s="144"/>
     </row>
     <row r="265" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C265" s="145"/>
-      <c r="D265" s="145"/>
-      <c r="E265" s="145"/>
-      <c r="F265" s="145"/>
+      <c r="C265" s="144"/>
+      <c r="D265" s="144"/>
+      <c r="E265" s="144"/>
+      <c r="F265" s="144"/>
     </row>
     <row r="266" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C266" s="145"/>
-      <c r="D266" s="145"/>
-      <c r="E266" s="145"/>
-      <c r="F266" s="145"/>
+      <c r="C266" s="144"/>
+      <c r="D266" s="144"/>
+      <c r="E266" s="144"/>
+      <c r="F266" s="144"/>
     </row>
     <row r="267" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C267" s="145"/>
-      <c r="D267" s="145"/>
-      <c r="E267" s="145"/>
-      <c r="F267" s="145"/>
+      <c r="C267" s="144"/>
+      <c r="D267" s="144"/>
+      <c r="E267" s="144"/>
+      <c r="F267" s="144"/>
     </row>
     <row r="268" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C268" s="145"/>
-      <c r="D268" s="145"/>
-      <c r="E268" s="145"/>
-      <c r="F268" s="145"/>
+      <c r="C268" s="144"/>
+      <c r="D268" s="144"/>
+      <c r="E268" s="144"/>
+      <c r="F268" s="144"/>
     </row>
     <row r="269" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C269" s="145"/>
-      <c r="D269" s="145"/>
-      <c r="E269" s="145"/>
-      <c r="F269" s="145"/>
+      <c r="C269" s="144"/>
+      <c r="D269" s="144"/>
+      <c r="E269" s="144"/>
+      <c r="F269" s="144"/>
     </row>
     <row r="270" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C270" s="145"/>
-      <c r="D270" s="145"/>
-      <c r="E270" s="145"/>
-      <c r="F270" s="145"/>
+      <c r="C270" s="144"/>
+      <c r="D270" s="144"/>
+      <c r="E270" s="144"/>
+      <c r="F270" s="144"/>
     </row>
     <row r="271" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C271" s="145"/>
-      <c r="D271" s="145"/>
-      <c r="E271" s="145"/>
-      <c r="F271" s="145"/>
+      <c r="C271" s="144"/>
+      <c r="D271" s="144"/>
+      <c r="E271" s="144"/>
+      <c r="F271" s="144"/>
     </row>
     <row r="272" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C272" s="145"/>
-      <c r="D272" s="145"/>
-      <c r="E272" s="145"/>
-      <c r="F272" s="145"/>
+      <c r="C272" s="144"/>
+      <c r="D272" s="144"/>
+      <c r="E272" s="144"/>
+      <c r="F272" s="144"/>
     </row>
     <row r="273" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C273" s="145"/>
-      <c r="D273" s="145"/>
-      <c r="E273" s="145"/>
-      <c r="F273" s="145"/>
+      <c r="C273" s="144"/>
+      <c r="D273" s="144"/>
+      <c r="E273" s="144"/>
+      <c r="F273" s="144"/>
     </row>
     <row r="274" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C274" s="145"/>
-      <c r="D274" s="145"/>
-      <c r="E274" s="145"/>
-      <c r="F274" s="145"/>
+      <c r="C274" s="144"/>
+      <c r="D274" s="144"/>
+      <c r="E274" s="144"/>
+      <c r="F274" s="144"/>
     </row>
     <row r="275" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C275" s="145"/>
-      <c r="D275" s="145"/>
-      <c r="E275" s="145"/>
-      <c r="F275" s="145"/>
+      <c r="C275" s="144"/>
+      <c r="D275" s="144"/>
+      <c r="E275" s="144"/>
+      <c r="F275" s="144"/>
     </row>
     <row r="276" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C276" s="145"/>
-      <c r="D276" s="145"/>
-      <c r="E276" s="145"/>
-      <c r="F276" s="145"/>
+      <c r="C276" s="144"/>
+      <c r="D276" s="144"/>
+      <c r="E276" s="144"/>
+      <c r="F276" s="144"/>
     </row>
     <row r="277" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C277" s="145"/>
-      <c r="D277" s="145"/>
-      <c r="E277" s="145"/>
-      <c r="F277" s="145"/>
+      <c r="C277" s="144"/>
+      <c r="D277" s="144"/>
+      <c r="E277" s="144"/>
+      <c r="F277" s="144"/>
     </row>
     <row r="278" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C278" s="145"/>
-      <c r="D278" s="145"/>
-      <c r="E278" s="145"/>
-      <c r="F278" s="145"/>
+      <c r="C278" s="144"/>
+      <c r="D278" s="144"/>
+      <c r="E278" s="144"/>
+      <c r="F278" s="144"/>
     </row>
     <row r="279" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C279" s="145"/>
-      <c r="D279" s="145"/>
-      <c r="E279" s="145"/>
-      <c r="F279" s="145"/>
+      <c r="C279" s="144"/>
+      <c r="D279" s="144"/>
+      <c r="E279" s="144"/>
+      <c r="F279" s="144"/>
     </row>
     <row r="280" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C280" s="145"/>
-      <c r="D280" s="145"/>
-      <c r="E280" s="145"/>
-      <c r="F280" s="145"/>
+      <c r="C280" s="144"/>
+      <c r="D280" s="144"/>
+      <c r="E280" s="144"/>
+      <c r="F280" s="144"/>
     </row>
     <row r="281" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C281" s="145"/>
-      <c r="D281" s="145"/>
-      <c r="E281" s="145"/>
-      <c r="F281" s="145"/>
+      <c r="C281" s="144"/>
+      <c r="D281" s="144"/>
+      <c r="E281" s="144"/>
+      <c r="F281" s="144"/>
     </row>
     <row r="282" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C282" s="145"/>
-      <c r="D282" s="145"/>
-      <c r="E282" s="145"/>
-      <c r="F282" s="145"/>
+      <c r="C282" s="144"/>
+      <c r="D282" s="144"/>
+      <c r="E282" s="144"/>
+      <c r="F282" s="144"/>
     </row>
     <row r="283" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C283" s="145"/>
-      <c r="D283" s="145"/>
-      <c r="E283" s="145"/>
-      <c r="F283" s="145"/>
+      <c r="C283" s="144"/>
+      <c r="D283" s="144"/>
+      <c r="E283" s="144"/>
+      <c r="F283" s="144"/>
     </row>
     <row r="284" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C284" s="145"/>
-      <c r="D284" s="145"/>
-      <c r="E284" s="145"/>
-      <c r="F284" s="145"/>
+      <c r="C284" s="144"/>
+      <c r="D284" s="144"/>
+      <c r="E284" s="144"/>
+      <c r="F284" s="144"/>
     </row>
     <row r="285" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C285" s="145"/>
-      <c r="D285" s="145"/>
-      <c r="E285" s="145"/>
-      <c r="F285" s="145"/>
+      <c r="C285" s="144"/>
+      <c r="D285" s="144"/>
+      <c r="E285" s="144"/>
+      <c r="F285" s="144"/>
     </row>
     <row r="286" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C286" s="145"/>
-      <c r="D286" s="145"/>
-      <c r="E286" s="145"/>
-      <c r="F286" s="145"/>
+      <c r="C286" s="144"/>
+      <c r="D286" s="144"/>
+      <c r="E286" s="144"/>
+      <c r="F286" s="144"/>
     </row>
     <row r="287" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C287" s="145"/>
-      <c r="D287" s="145"/>
-      <c r="E287" s="145"/>
-      <c r="F287" s="145"/>
+      <c r="C287" s="144"/>
+      <c r="D287" s="144"/>
+      <c r="E287" s="144"/>
+      <c r="F287" s="144"/>
     </row>
     <row r="288" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C288" s="145"/>
-      <c r="D288" s="145"/>
-      <c r="E288" s="145"/>
-      <c r="F288" s="145"/>
+      <c r="C288" s="144"/>
+      <c r="D288" s="144"/>
+      <c r="E288" s="144"/>
+      <c r="F288" s="144"/>
     </row>
     <row r="289" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C289" s="145"/>
-      <c r="D289" s="145"/>
-      <c r="E289" s="145"/>
-      <c r="F289" s="145"/>
+      <c r="C289" s="144"/>
+      <c r="D289" s="144"/>
+      <c r="E289" s="144"/>
+      <c r="F289" s="144"/>
     </row>
     <row r="290" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C290" s="145"/>
-      <c r="D290" s="145"/>
-      <c r="E290" s="145"/>
-      <c r="F290" s="145"/>
+      <c r="C290" s="144"/>
+      <c r="D290" s="144"/>
+      <c r="E290" s="144"/>
+      <c r="F290" s="144"/>
     </row>
     <row r="291" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C291" s="145"/>
-      <c r="D291" s="145"/>
-      <c r="E291" s="145"/>
-      <c r="F291" s="145"/>
+      <c r="C291" s="144"/>
+      <c r="D291" s="144"/>
+      <c r="E291" s="144"/>
+      <c r="F291" s="144"/>
     </row>
     <row r="292" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C292" s="145"/>
-      <c r="D292" s="145"/>
-      <c r="E292" s="145"/>
-      <c r="F292" s="145"/>
+      <c r="C292" s="144"/>
+      <c r="D292" s="144"/>
+      <c r="E292" s="144"/>
+      <c r="F292" s="144"/>
     </row>
     <row r="293" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C293" s="145"/>
-      <c r="D293" s="145"/>
-      <c r="E293" s="145"/>
-      <c r="F293" s="145"/>
+      <c r="C293" s="144"/>
+      <c r="D293" s="144"/>
+      <c r="E293" s="144"/>
+      <c r="F293" s="144"/>
     </row>
     <row r="294" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C294" s="145"/>
-      <c r="D294" s="145"/>
-      <c r="E294" s="145"/>
-      <c r="F294" s="145"/>
+      <c r="C294" s="144"/>
+      <c r="D294" s="144"/>
+      <c r="E294" s="144"/>
+      <c r="F294" s="144"/>
     </row>
     <row r="295" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C295" s="145"/>
-      <c r="D295" s="145"/>
-      <c r="E295" s="145"/>
-      <c r="F295" s="145"/>
+      <c r="C295" s="144"/>
+      <c r="D295" s="144"/>
+      <c r="E295" s="144"/>
+      <c r="F295" s="144"/>
     </row>
     <row r="296" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C296" s="145"/>
-      <c r="D296" s="145"/>
-      <c r="E296" s="145"/>
-      <c r="F296" s="145"/>
+      <c r="C296" s="144"/>
+      <c r="D296" s="144"/>
+      <c r="E296" s="144"/>
+      <c r="F296" s="144"/>
     </row>
     <row r="297" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C297" s="145"/>
-      <c r="D297" s="145"/>
-      <c r="E297" s="145"/>
-      <c r="F297" s="145"/>
+      <c r="C297" s="144"/>
+      <c r="D297" s="144"/>
+      <c r="E297" s="144"/>
+      <c r="F297" s="144"/>
     </row>
     <row r="298" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C298" s="145"/>
-      <c r="D298" s="145"/>
-      <c r="E298" s="145"/>
-      <c r="F298" s="145"/>
+      <c r="C298" s="144"/>
+      <c r="D298" s="144"/>
+      <c r="E298" s="144"/>
+      <c r="F298" s="144"/>
     </row>
     <row r="299" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C299" s="145"/>
-      <c r="D299" s="145"/>
-      <c r="E299" s="145"/>
-      <c r="F299" s="145"/>
+      <c r="C299" s="144"/>
+      <c r="D299" s="144"/>
+      <c r="E299" s="144"/>
+      <c r="F299" s="144"/>
     </row>
     <row r="300" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C300" s="145"/>
-      <c r="D300" s="145"/>
-      <c r="E300" s="145"/>
-      <c r="F300" s="145"/>
+      <c r="C300" s="144"/>
+      <c r="D300" s="144"/>
+      <c r="E300" s="144"/>
+      <c r="F300" s="144"/>
     </row>
     <row r="301" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C301" s="145"/>
-      <c r="D301" s="145"/>
-      <c r="E301" s="145"/>
-      <c r="F301" s="145"/>
+      <c r="C301" s="144"/>
+      <c r="D301" s="144"/>
+      <c r="E301" s="144"/>
+      <c r="F301" s="144"/>
     </row>
     <row r="302" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C302" s="145"/>
-      <c r="D302" s="145"/>
-      <c r="E302" s="145"/>
-      <c r="F302" s="145"/>
+      <c r="C302" s="144"/>
+      <c r="D302" s="144"/>
+      <c r="E302" s="144"/>
+      <c r="F302" s="144"/>
     </row>
     <row r="303" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C303" s="145"/>
-      <c r="D303" s="145"/>
-      <c r="E303" s="145"/>
-      <c r="F303" s="145"/>
+      <c r="C303" s="144"/>
+      <c r="D303" s="144"/>
+      <c r="E303" s="144"/>
+      <c r="F303" s="144"/>
     </row>
     <row r="304" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C304" s="145"/>
-      <c r="D304" s="145"/>
-      <c r="E304" s="145"/>
-      <c r="F304" s="145"/>
+      <c r="C304" s="144"/>
+      <c r="D304" s="144"/>
+      <c r="E304" s="144"/>
+      <c r="F304" s="144"/>
     </row>
     <row r="305" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C305" s="145"/>
-      <c r="D305" s="145"/>
-      <c r="E305" s="145"/>
-      <c r="F305" s="145"/>
+      <c r="C305" s="144"/>
+      <c r="D305" s="144"/>
+      <c r="E305" s="144"/>
+      <c r="F305" s="144"/>
     </row>
     <row r="306" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C306" s="145"/>
-      <c r="D306" s="145"/>
-      <c r="E306" s="145"/>
-      <c r="F306" s="145"/>
+      <c r="C306" s="144"/>
+      <c r="D306" s="144"/>
+      <c r="E306" s="144"/>
+      <c r="F306" s="144"/>
     </row>
     <row r="307" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C307" s="145"/>
-      <c r="D307" s="145"/>
-      <c r="E307" s="145"/>
-      <c r="F307" s="145"/>
+      <c r="C307" s="144"/>
+      <c r="D307" s="144"/>
+      <c r="E307" s="144"/>
+      <c r="F307" s="144"/>
     </row>
     <row r="308" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C308" s="145"/>
-      <c r="D308" s="145"/>
-      <c r="E308" s="145"/>
-      <c r="F308" s="145"/>
+      <c r="C308" s="144"/>
+      <c r="D308" s="144"/>
+      <c r="E308" s="144"/>
+      <c r="F308" s="144"/>
     </row>
     <row r="309" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C309" s="145"/>
-      <c r="D309" s="145"/>
-      <c r="E309" s="145"/>
-      <c r="F309" s="145"/>
+      <c r="C309" s="144"/>
+      <c r="D309" s="144"/>
+      <c r="E309" s="144"/>
+      <c r="F309" s="144"/>
     </row>
     <row r="310" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C310" s="145"/>
-      <c r="D310" s="145"/>
-      <c r="E310" s="145"/>
-      <c r="F310" s="145"/>
+      <c r="C310" s="144"/>
+      <c r="D310" s="144"/>
+      <c r="E310" s="144"/>
+      <c r="F310" s="144"/>
     </row>
     <row r="311" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C311" s="145"/>
-      <c r="D311" s="145"/>
-      <c r="E311" s="145"/>
-      <c r="F311" s="145"/>
+      <c r="C311" s="144"/>
+      <c r="D311" s="144"/>
+      <c r="E311" s="144"/>
+      <c r="F311" s="144"/>
     </row>
     <row r="312" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C312" s="145"/>
-      <c r="D312" s="145"/>
-      <c r="E312" s="145"/>
-      <c r="F312" s="145"/>
+      <c r="C312" s="144"/>
+      <c r="D312" s="144"/>
+      <c r="E312" s="144"/>
+      <c r="F312" s="144"/>
     </row>
     <row r="313" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C313" s="145"/>
-      <c r="D313" s="145"/>
-      <c r="E313" s="145"/>
-      <c r="F313" s="145"/>
+      <c r="C313" s="144"/>
+      <c r="D313" s="144"/>
+      <c r="E313" s="144"/>
+      <c r="F313" s="144"/>
     </row>
     <row r="314" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C314" s="145"/>
-      <c r="D314" s="145"/>
-      <c r="E314" s="145"/>
-      <c r="F314" s="145"/>
+      <c r="C314" s="144"/>
+      <c r="D314" s="144"/>
+      <c r="E314" s="144"/>
+      <c r="F314" s="144"/>
     </row>
     <row r="315" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C315" s="145"/>
-      <c r="D315" s="145"/>
-      <c r="E315" s="145"/>
-      <c r="F315" s="145"/>
+      <c r="C315" s="144"/>
+      <c r="D315" s="144"/>
+      <c r="E315" s="144"/>
+      <c r="F315" s="144"/>
     </row>
     <row r="316" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C316" s="145"/>
-      <c r="D316" s="145"/>
-      <c r="E316" s="145"/>
-      <c r="F316" s="145"/>
+      <c r="C316" s="144"/>
+      <c r="D316" s="144"/>
+      <c r="E316" s="144"/>
+      <c r="F316" s="144"/>
     </row>
     <row r="317" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C317" s="145"/>
-      <c r="D317" s="145"/>
-      <c r="E317" s="145"/>
-      <c r="F317" s="145"/>
+      <c r="C317" s="144"/>
+      <c r="D317" s="144"/>
+      <c r="E317" s="144"/>
+      <c r="F317" s="144"/>
     </row>
     <row r="318" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C318" s="145"/>
-      <c r="D318" s="145"/>
-      <c r="E318" s="145"/>
-      <c r="F318" s="145"/>
+      <c r="C318" s="144"/>
+      <c r="D318" s="144"/>
+      <c r="E318" s="144"/>
+      <c r="F318" s="144"/>
     </row>
     <row r="319" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C319" s="145"/>
-      <c r="D319" s="145"/>
-      <c r="E319" s="145"/>
-      <c r="F319" s="145"/>
+      <c r="C319" s="144"/>
+      <c r="D319" s="144"/>
+      <c r="E319" s="144"/>
+      <c r="F319" s="144"/>
     </row>
     <row r="320" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C320" s="145"/>
-      <c r="D320" s="145"/>
-      <c r="E320" s="145"/>
-      <c r="F320" s="145"/>
+      <c r="C320" s="144"/>
+      <c r="D320" s="144"/>
+      <c r="E320" s="144"/>
+      <c r="F320" s="144"/>
     </row>
     <row r="321" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C321" s="145"/>
-      <c r="D321" s="145"/>
-      <c r="E321" s="145"/>
-      <c r="F321" s="145"/>
+      <c r="C321" s="144"/>
+      <c r="D321" s="144"/>
+      <c r="E321" s="144"/>
+      <c r="F321" s="144"/>
     </row>
     <row r="322" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C322" s="145"/>
-      <c r="D322" s="145"/>
-      <c r="E322" s="145"/>
-      <c r="F322" s="145"/>
+      <c r="C322" s="144"/>
+      <c r="D322" s="144"/>
+      <c r="E322" s="144"/>
+      <c r="F322" s="144"/>
     </row>
     <row r="323" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C323" s="145"/>
-      <c r="D323" s="145"/>
-      <c r="E323" s="145"/>
-      <c r="F323" s="145"/>
+      <c r="C323" s="144"/>
+      <c r="D323" s="144"/>
+      <c r="E323" s="144"/>
+      <c r="F323" s="144"/>
     </row>
     <row r="324" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C324" s="145"/>
-      <c r="D324" s="145"/>
-      <c r="E324" s="145"/>
-      <c r="F324" s="145"/>
+      <c r="C324" s="144"/>
+      <c r="D324" s="144"/>
+      <c r="E324" s="144"/>
+      <c r="F324" s="144"/>
     </row>
     <row r="325" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C325" s="145"/>
-      <c r="D325" s="145"/>
-      <c r="E325" s="145"/>
-      <c r="F325" s="145"/>
+      <c r="C325" s="144"/>
+      <c r="D325" s="144"/>
+      <c r="E325" s="144"/>
+      <c r="F325" s="144"/>
     </row>
     <row r="326" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C326" s="145"/>
-      <c r="D326" s="145"/>
-      <c r="E326" s="145"/>
-      <c r="F326" s="145"/>
+      <c r="C326" s="144"/>
+      <c r="D326" s="144"/>
+      <c r="E326" s="144"/>
+      <c r="F326" s="144"/>
     </row>
     <row r="327" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C327" s="145"/>
-      <c r="D327" s="145"/>
-      <c r="E327" s="145"/>
-      <c r="F327" s="145"/>
+      <c r="C327" s="144"/>
+      <c r="D327" s="144"/>
+      <c r="E327" s="144"/>
+      <c r="F327" s="144"/>
     </row>
     <row r="328" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C328" s="145"/>
-      <c r="D328" s="145"/>
-      <c r="E328" s="145"/>
-      <c r="F328" s="145"/>
+      <c r="C328" s="144"/>
+      <c r="D328" s="144"/>
+      <c r="E328" s="144"/>
+      <c r="F328" s="144"/>
     </row>
     <row r="329" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C329" s="145"/>
-      <c r="D329" s="145"/>
-      <c r="E329" s="145"/>
-      <c r="F329" s="145"/>
+      <c r="C329" s="144"/>
+      <c r="D329" s="144"/>
+      <c r="E329" s="144"/>
+      <c r="F329" s="144"/>
     </row>
     <row r="330" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C330" s="145"/>
-      <c r="D330" s="145"/>
-      <c r="E330" s="145"/>
-      <c r="F330" s="145"/>
+      <c r="C330" s="144"/>
+      <c r="D330" s="144"/>
+      <c r="E330" s="144"/>
+      <c r="F330" s="144"/>
     </row>
     <row r="331" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C331" s="145"/>
-      <c r="D331" s="145"/>
-      <c r="E331" s="145"/>
-      <c r="F331" s="145"/>
+      <c r="C331" s="144"/>
+      <c r="D331" s="144"/>
+      <c r="E331" s="144"/>
+      <c r="F331" s="144"/>
     </row>
     <row r="332" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C332" s="145"/>
-      <c r="D332" s="145"/>
-      <c r="E332" s="145"/>
-      <c r="F332" s="145"/>
+      <c r="C332" s="144"/>
+      <c r="D332" s="144"/>
+      <c r="E332" s="144"/>
+      <c r="F332" s="144"/>
     </row>
     <row r="333" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C333" s="145"/>
-      <c r="D333" s="145"/>
-      <c r="E333" s="145"/>
-      <c r="F333" s="145"/>
+      <c r="C333" s="144"/>
+      <c r="D333" s="144"/>
+      <c r="E333" s="144"/>
+      <c r="F333" s="144"/>
     </row>
     <row r="334" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C334" s="145"/>
-      <c r="D334" s="145"/>
-      <c r="E334" s="145"/>
-      <c r="F334" s="145"/>
+      <c r="C334" s="144"/>
+      <c r="D334" s="144"/>
+      <c r="E334" s="144"/>
+      <c r="F334" s="144"/>
     </row>
     <row r="335" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C335" s="145"/>
-      <c r="D335" s="145"/>
-      <c r="E335" s="145"/>
-      <c r="F335" s="145"/>
+      <c r="C335" s="144"/>
+      <c r="D335" s="144"/>
+      <c r="E335" s="144"/>
+      <c r="F335" s="144"/>
     </row>
     <row r="336" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C336" s="145"/>
-      <c r="D336" s="145"/>
-      <c r="E336" s="145"/>
-      <c r="F336" s="145"/>
+      <c r="C336" s="144"/>
+      <c r="D336" s="144"/>
+      <c r="E336" s="144"/>
+      <c r="F336" s="144"/>
     </row>
     <row r="337" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C337" s="145"/>
-      <c r="D337" s="145"/>
-      <c r="E337" s="145"/>
-      <c r="F337" s="145"/>
+      <c r="C337" s="144"/>
+      <c r="D337" s="144"/>
+      <c r="E337" s="144"/>
+      <c r="F337" s="144"/>
     </row>
     <row r="338" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C338" s="145"/>
-      <c r="D338" s="145"/>
-      <c r="E338" s="145"/>
-      <c r="F338" s="145"/>
+      <c r="C338" s="144"/>
+      <c r="D338" s="144"/>
+      <c r="E338" s="144"/>
+      <c r="F338" s="144"/>
     </row>
     <row r="339" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C339" s="145"/>
-      <c r="D339" s="145"/>
-      <c r="E339" s="145"/>
-      <c r="F339" s="145"/>
+      <c r="C339" s="144"/>
+      <c r="D339" s="144"/>
+      <c r="E339" s="144"/>
+      <c r="F339" s="144"/>
     </row>
     <row r="340" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C340" s="145"/>
-      <c r="D340" s="145"/>
-      <c r="E340" s="145"/>
-      <c r="F340" s="145"/>
+      <c r="C340" s="144"/>
+      <c r="D340" s="144"/>
+      <c r="E340" s="144"/>
+      <c r="F340" s="144"/>
     </row>
     <row r="341" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C341" s="145"/>
-      <c r="D341" s="145"/>
-      <c r="E341" s="145"/>
-      <c r="F341" s="145"/>
+      <c r="C341" s="144"/>
+      <c r="D341" s="144"/>
+      <c r="E341" s="144"/>
+      <c r="F341" s="144"/>
     </row>
     <row r="342" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C342" s="145"/>
-      <c r="D342" s="145"/>
-      <c r="E342" s="145"/>
-      <c r="F342" s="145"/>
+      <c r="C342" s="144"/>
+      <c r="D342" s="144"/>
+      <c r="E342" s="144"/>
+      <c r="F342" s="144"/>
     </row>
     <row r="343" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C343" s="145"/>
-      <c r="D343" s="145"/>
-      <c r="E343" s="145"/>
-      <c r="F343" s="145"/>
+      <c r="C343" s="144"/>
+      <c r="D343" s="144"/>
+      <c r="E343" s="144"/>
+      <c r="F343" s="144"/>
     </row>
     <row r="344" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C344" s="145"/>
-      <c r="D344" s="145"/>
-      <c r="E344" s="145"/>
-      <c r="F344" s="145"/>
+      <c r="C344" s="144"/>
+      <c r="D344" s="144"/>
+      <c r="E344" s="144"/>
+      <c r="F344" s="144"/>
     </row>
     <row r="345" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C345" s="145"/>
-      <c r="D345" s="145"/>
-      <c r="E345" s="145"/>
-      <c r="F345" s="145"/>
+      <c r="C345" s="144"/>
+      <c r="D345" s="144"/>
+      <c r="E345" s="144"/>
+      <c r="F345" s="144"/>
     </row>
     <row r="346" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C346" s="145"/>
-      <c r="D346" s="145"/>
-      <c r="E346" s="145"/>
-      <c r="F346" s="145"/>
+      <c r="C346" s="144"/>
+      <c r="D346" s="144"/>
+      <c r="E346" s="144"/>
+      <c r="F346" s="144"/>
     </row>
     <row r="347" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C347" s="145"/>
-      <c r="D347" s="145"/>
-      <c r="E347" s="145"/>
-      <c r="F347" s="145"/>
+      <c r="C347" s="144"/>
+      <c r="D347" s="144"/>
+      <c r="E347" s="144"/>
+      <c r="F347" s="144"/>
     </row>
     <row r="348" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C348" s="145"/>
-      <c r="D348" s="145"/>
-      <c r="E348" s="145"/>
-      <c r="F348" s="145"/>
+      <c r="C348" s="144"/>
+      <c r="D348" s="144"/>
+      <c r="E348" s="144"/>
+      <c r="F348" s="144"/>
     </row>
     <row r="349" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C349" s="145"/>
-      <c r="D349" s="145"/>
-      <c r="E349" s="145"/>
-      <c r="F349" s="145"/>
+      <c r="C349" s="144"/>
+      <c r="D349" s="144"/>
+      <c r="E349" s="144"/>
+      <c r="F349" s="144"/>
     </row>
     <row r="350" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C350" s="145"/>
-      <c r="D350" s="145"/>
-      <c r="E350" s="145"/>
-      <c r="F350" s="145"/>
+      <c r="C350" s="144"/>
+      <c r="D350" s="144"/>
+      <c r="E350" s="144"/>
+      <c r="F350" s="144"/>
     </row>
     <row r="351" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C351" s="145"/>
-      <c r="D351" s="145"/>
-      <c r="E351" s="145"/>
-      <c r="F351" s="145"/>
+      <c r="C351" s="144"/>
+      <c r="D351" s="144"/>
+      <c r="E351" s="144"/>
+      <c r="F351" s="144"/>
     </row>
     <row r="352" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C352" s="145"/>
-      <c r="D352" s="145"/>
-      <c r="E352" s="145"/>
-      <c r="F352" s="145"/>
+      <c r="C352" s="144"/>
+      <c r="D352" s="144"/>
+      <c r="E352" s="144"/>
+      <c r="F352" s="144"/>
     </row>
     <row r="353" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C353" s="145"/>
-      <c r="D353" s="145"/>
-      <c r="E353" s="145"/>
-      <c r="F353" s="145"/>
+      <c r="C353" s="144"/>
+      <c r="D353" s="144"/>
+      <c r="E353" s="144"/>
+      <c r="F353" s="144"/>
     </row>
     <row r="354" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C354" s="145"/>
-      <c r="D354" s="145"/>
-      <c r="E354" s="145"/>
-      <c r="F354" s="145"/>
+      <c r="C354" s="144"/>
+      <c r="D354" s="144"/>
+      <c r="E354" s="144"/>
+      <c r="F354" s="144"/>
     </row>
     <row r="355" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C355" s="145"/>
-      <c r="D355" s="145"/>
-      <c r="E355" s="145"/>
-      <c r="F355" s="145"/>
+      <c r="C355" s="144"/>
+      <c r="D355" s="144"/>
+      <c r="E355" s="144"/>
+      <c r="F355" s="144"/>
     </row>
     <row r="356" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C356" s="145"/>
-      <c r="D356" s="145"/>
-      <c r="E356" s="145"/>
-      <c r="F356" s="145"/>
+      <c r="C356" s="144"/>
+      <c r="D356" s="144"/>
+      <c r="E356" s="144"/>
+      <c r="F356" s="144"/>
     </row>
     <row r="357" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C357" s="145"/>
-      <c r="D357" s="145"/>
-      <c r="E357" s="145"/>
-      <c r="F357" s="145"/>
+      <c r="C357" s="144"/>
+      <c r="D357" s="144"/>
+      <c r="E357" s="144"/>
+      <c r="F357" s="144"/>
     </row>
     <row r="358" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C358" s="145"/>
-      <c r="D358" s="145"/>
-      <c r="E358" s="145"/>
-      <c r="F358" s="145"/>
+      <c r="C358" s="144"/>
+      <c r="D358" s="144"/>
+      <c r="E358" s="144"/>
+      <c r="F358" s="144"/>
     </row>
     <row r="359" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C359" s="145"/>
-      <c r="D359" s="145"/>
-      <c r="E359" s="145"/>
-      <c r="F359" s="145"/>
+      <c r="C359" s="144"/>
+      <c r="D359" s="144"/>
+      <c r="E359" s="144"/>
+      <c r="F359" s="144"/>
     </row>
     <row r="360" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C360" s="145"/>
-      <c r="D360" s="145"/>
-      <c r="E360" s="145"/>
-      <c r="F360" s="145"/>
+      <c r="C360" s="144"/>
+      <c r="D360" s="144"/>
+      <c r="E360" s="144"/>
+      <c r="F360" s="144"/>
     </row>
     <row r="361" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C361" s="145"/>
-      <c r="D361" s="145"/>
-      <c r="E361" s="145"/>
-      <c r="F361" s="145"/>
+      <c r="C361" s="144"/>
+      <c r="D361" s="144"/>
+      <c r="E361" s="144"/>
+      <c r="F361" s="144"/>
     </row>
     <row r="362" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C362" s="145"/>
-      <c r="D362" s="145"/>
-      <c r="E362" s="145"/>
-      <c r="F362" s="145"/>
+      <c r="C362" s="144"/>
+      <c r="D362" s="144"/>
+      <c r="E362" s="144"/>
+      <c r="F362" s="144"/>
     </row>
     <row r="363" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C363" s="145"/>
-      <c r="D363" s="145"/>
-      <c r="E363" s="145"/>
-      <c r="F363" s="145"/>
+      <c r="C363" s="144"/>
+      <c r="D363" s="144"/>
+      <c r="E363" s="144"/>
+      <c r="F363" s="144"/>
     </row>
     <row r="364" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C364" s="145"/>
-      <c r="D364" s="145"/>
-      <c r="E364" s="145"/>
-      <c r="F364" s="145"/>
+      <c r="C364" s="144"/>
+      <c r="D364" s="144"/>
+      <c r="E364" s="144"/>
+      <c r="F364" s="144"/>
     </row>
     <row r="365" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C365" s="145"/>
-      <c r="D365" s="145"/>
-      <c r="E365" s="145"/>
-      <c r="F365" s="145"/>
+      <c r="C365" s="144"/>
+      <c r="D365" s="144"/>
+      <c r="E365" s="144"/>
+      <c r="F365" s="144"/>
     </row>
     <row r="366" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C366" s="145"/>
-      <c r="D366" s="145"/>
-      <c r="E366" s="145"/>
-      <c r="F366" s="145"/>
+      <c r="C366" s="144"/>
+      <c r="D366" s="144"/>
+      <c r="E366" s="144"/>
+      <c r="F366" s="144"/>
     </row>
     <row r="367" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C367" s="145"/>
-      <c r="D367" s="145"/>
-      <c r="E367" s="145"/>
-      <c r="F367" s="145"/>
+      <c r="C367" s="144"/>
+      <c r="D367" s="144"/>
+      <c r="E367" s="144"/>
+      <c r="F367" s="144"/>
     </row>
     <row r="368" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C368" s="145"/>
-      <c r="D368" s="145"/>
-      <c r="E368" s="145"/>
-      <c r="F368" s="145"/>
+      <c r="C368" s="144"/>
+      <c r="D368" s="144"/>
+      <c r="E368" s="144"/>
+      <c r="F368" s="144"/>
     </row>
     <row r="369" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C369" s="145"/>
-      <c r="D369" s="145"/>
-      <c r="E369" s="145"/>
-      <c r="F369" s="145"/>
+      <c r="C369" s="144"/>
+      <c r="D369" s="144"/>
+      <c r="E369" s="144"/>
+      <c r="F369" s="144"/>
     </row>
     <row r="370" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C370" s="145"/>
-      <c r="D370" s="145"/>
-      <c r="E370" s="145"/>
-      <c r="F370" s="145"/>
+      <c r="C370" s="144"/>
+      <c r="D370" s="144"/>
+      <c r="E370" s="144"/>
+      <c r="F370" s="144"/>
     </row>
     <row r="371" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C371" s="145"/>
-      <c r="D371" s="145"/>
-      <c r="E371" s="145"/>
-      <c r="F371" s="145"/>
+      <c r="C371" s="144"/>
+      <c r="D371" s="144"/>
+      <c r="E371" s="144"/>
+      <c r="F371" s="144"/>
     </row>
     <row r="372" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C372" s="145"/>
-      <c r="D372" s="145"/>
-      <c r="E372" s="145"/>
-      <c r="F372" s="145"/>
+      <c r="C372" s="144"/>
+      <c r="D372" s="144"/>
+      <c r="E372" s="144"/>
+      <c r="F372" s="144"/>
     </row>
     <row r="373" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C373" s="145"/>
-      <c r="D373" s="145"/>
-      <c r="E373" s="145"/>
-      <c r="F373" s="145"/>
+      <c r="C373" s="144"/>
+      <c r="D373" s="144"/>
+      <c r="E373" s="144"/>
+      <c r="F373" s="144"/>
     </row>
     <row r="374" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C374" s="145"/>
-      <c r="D374" s="145"/>
-      <c r="E374" s="145"/>
-      <c r="F374" s="145"/>
+      <c r="C374" s="144"/>
+      <c r="D374" s="144"/>
+      <c r="E374" s="144"/>
+      <c r="F374" s="144"/>
     </row>
     <row r="375" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C375" s="145"/>
-      <c r="D375" s="145"/>
-      <c r="E375" s="145"/>
-      <c r="F375" s="145"/>
+      <c r="C375" s="144"/>
+      <c r="D375" s="144"/>
+      <c r="E375" s="144"/>
+      <c r="F375" s="144"/>
     </row>
     <row r="376" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C376" s="145"/>
-      <c r="D376" s="145"/>
-      <c r="E376" s="145"/>
-      <c r="F376" s="145"/>
+      <c r="C376" s="144"/>
+      <c r="D376" s="144"/>
+      <c r="E376" s="144"/>
+      <c r="F376" s="144"/>
     </row>
     <row r="377" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C377" s="145"/>
-      <c r="D377" s="145"/>
-      <c r="E377" s="145"/>
-      <c r="F377" s="145"/>
+      <c r="C377" s="144"/>
+      <c r="D377" s="144"/>
+      <c r="E377" s="144"/>
+      <c r="F377" s="144"/>
     </row>
     <row r="378" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C378" s="145"/>
-      <c r="D378" s="145"/>
-      <c r="E378" s="145"/>
-      <c r="F378" s="145"/>
+      <c r="C378" s="144"/>
+      <c r="D378" s="144"/>
+      <c r="E378" s="144"/>
+      <c r="F378" s="144"/>
     </row>
     <row r="379" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C379" s="145"/>
-      <c r="D379" s="145"/>
-      <c r="E379" s="145"/>
-      <c r="F379" s="145"/>
+      <c r="C379" s="144"/>
+      <c r="D379" s="144"/>
+      <c r="E379" s="144"/>
+      <c r="F379" s="144"/>
     </row>
     <row r="380" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C380" s="145"/>
-      <c r="D380" s="145"/>
-      <c r="E380" s="145"/>
-      <c r="F380" s="145"/>
+      <c r="C380" s="144"/>
+      <c r="D380" s="144"/>
+      <c r="E380" s="144"/>
+      <c r="F380" s="144"/>
     </row>
     <row r="381" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C381" s="145"/>
-      <c r="D381" s="145"/>
-      <c r="E381" s="145"/>
-      <c r="F381" s="145"/>
+      <c r="C381" s="144"/>
+      <c r="D381" s="144"/>
+      <c r="E381" s="144"/>
+      <c r="F381" s="144"/>
     </row>
     <row r="382" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C382" s="145"/>
-      <c r="D382" s="145"/>
-      <c r="E382" s="145"/>
-      <c r="F382" s="145"/>
+      <c r="C382" s="144"/>
+      <c r="D382" s="144"/>
+      <c r="E382" s="144"/>
+      <c r="F382" s="144"/>
     </row>
     <row r="383" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C383" s="145"/>
-      <c r="D383" s="145"/>
-      <c r="E383" s="145"/>
-      <c r="F383" s="145"/>
+      <c r="C383" s="144"/>
+      <c r="D383" s="144"/>
+      <c r="E383" s="144"/>
+      <c r="F383" s="144"/>
     </row>
     <row r="384" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C384" s="145"/>
-      <c r="D384" s="145"/>
-      <c r="E384" s="145"/>
-      <c r="F384" s="145"/>
+      <c r="C384" s="144"/>
+      <c r="D384" s="144"/>
+      <c r="E384" s="144"/>
+      <c r="F384" s="144"/>
     </row>
     <row r="385" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C385" s="145"/>
-      <c r="D385" s="145"/>
-      <c r="E385" s="145"/>
-      <c r="F385" s="145"/>
+      <c r="C385" s="144"/>
+      <c r="D385" s="144"/>
+      <c r="E385" s="144"/>
+      <c r="F385" s="144"/>
     </row>
     <row r="386" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C386" s="145"/>
-      <c r="D386" s="145"/>
-      <c r="E386" s="145"/>
-      <c r="F386" s="145"/>
+      <c r="C386" s="144"/>
+      <c r="D386" s="144"/>
+      <c r="E386" s="144"/>
+      <c r="F386" s="144"/>
     </row>
     <row r="387" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C387" s="145"/>
-      <c r="D387" s="145"/>
-      <c r="E387" s="145"/>
-      <c r="F387" s="145"/>
+      <c r="C387" s="144"/>
+      <c r="D387" s="144"/>
+      <c r="E387" s="144"/>
+      <c r="F387" s="144"/>
     </row>
     <row r="388" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C388" s="145"/>
-      <c r="D388" s="145"/>
-      <c r="E388" s="145"/>
-      <c r="F388" s="145"/>
+      <c r="C388" s="144"/>
+      <c r="D388" s="144"/>
+      <c r="E388" s="144"/>
+      <c r="F388" s="144"/>
     </row>
     <row r="389" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C389" s="145"/>
-      <c r="D389" s="145"/>
-      <c r="E389" s="145"/>
-      <c r="F389" s="145"/>
+      <c r="C389" s="144"/>
+      <c r="D389" s="144"/>
+      <c r="E389" s="144"/>
+      <c r="F389" s="144"/>
     </row>
     <row r="390" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C390" s="145"/>
-      <c r="D390" s="145"/>
-      <c r="E390" s="145"/>
-      <c r="F390" s="145"/>
+      <c r="C390" s="144"/>
+      <c r="D390" s="144"/>
+      <c r="E390" s="144"/>
+      <c r="F390" s="144"/>
     </row>
     <row r="391" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C391" s="145"/>
-      <c r="D391" s="145"/>
-      <c r="E391" s="145"/>
-      <c r="F391" s="145"/>
+      <c r="C391" s="144"/>
+      <c r="D391" s="144"/>
+      <c r="E391" s="144"/>
+      <c r="F391" s="144"/>
     </row>
     <row r="392" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C392" s="145"/>
-      <c r="D392" s="145"/>
-      <c r="E392" s="145"/>
-      <c r="F392" s="145"/>
+      <c r="C392" s="144"/>
+      <c r="D392" s="144"/>
+      <c r="E392" s="144"/>
+      <c r="F392" s="144"/>
     </row>
     <row r="393" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C393" s="145"/>
-      <c r="D393" s="145"/>
-      <c r="E393" s="145"/>
-      <c r="F393" s="145"/>
+      <c r="C393" s="144"/>
+      <c r="D393" s="144"/>
+      <c r="E393" s="144"/>
+      <c r="F393" s="144"/>
     </row>
     <row r="394" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C394" s="145"/>
-      <c r="D394" s="145"/>
-      <c r="E394" s="145"/>
-      <c r="F394" s="145"/>
+      <c r="C394" s="144"/>
+      <c r="D394" s="144"/>
+      <c r="E394" s="144"/>
+      <c r="F394" s="144"/>
     </row>
     <row r="395" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C395" s="145"/>
-      <c r="D395" s="145"/>
-      <c r="E395" s="145"/>
-      <c r="F395" s="145"/>
+      <c r="C395" s="144"/>
+      <c r="D395" s="144"/>
+      <c r="E395" s="144"/>
+      <c r="F395" s="144"/>
     </row>
     <row r="396" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C396" s="145"/>
-      <c r="D396" s="145"/>
-      <c r="E396" s="145"/>
-      <c r="F396" s="145"/>
+      <c r="C396" s="144"/>
+      <c r="D396" s="144"/>
+      <c r="E396" s="144"/>
+      <c r="F396" s="144"/>
     </row>
     <row r="397" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C397" s="145"/>
-      <c r="D397" s="145"/>
-      <c r="E397" s="145"/>
-      <c r="F397" s="145"/>
+      <c r="C397" s="144"/>
+      <c r="D397" s="144"/>
+      <c r="E397" s="144"/>
+      <c r="F397" s="144"/>
     </row>
     <row r="398" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C398" s="145"/>
-      <c r="D398" s="145"/>
-      <c r="E398" s="145"/>
-      <c r="F398" s="145"/>
+      <c r="C398" s="144"/>
+      <c r="D398" s="144"/>
+      <c r="E398" s="144"/>
+      <c r="F398" s="144"/>
     </row>
     <row r="399" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C399" s="145"/>
-      <c r="D399" s="145"/>
-      <c r="E399" s="145"/>
-      <c r="F399" s="145"/>
+      <c r="C399" s="144"/>
+      <c r="D399" s="144"/>
+      <c r="E399" s="144"/>
+      <c r="F399" s="144"/>
     </row>
     <row r="400" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C400" s="145"/>
-      <c r="D400" s="145"/>
-      <c r="E400" s="145"/>
-      <c r="F400" s="145"/>
+      <c r="C400" s="144"/>
+      <c r="D400" s="144"/>
+      <c r="E400" s="144"/>
+      <c r="F400" s="144"/>
     </row>
     <row r="401" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C401" s="145"/>
-      <c r="D401" s="145"/>
-      <c r="E401" s="145"/>
-      <c r="F401" s="145"/>
+      <c r="C401" s="144"/>
+      <c r="D401" s="144"/>
+      <c r="E401" s="144"/>
+      <c r="F401" s="144"/>
     </row>
     <row r="402" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C402" s="145"/>
-      <c r="D402" s="145"/>
-      <c r="E402" s="145"/>
-      <c r="F402" s="145"/>
+      <c r="C402" s="144"/>
+      <c r="D402" s="144"/>
+      <c r="E402" s="144"/>
+      <c r="F402" s="144"/>
     </row>
     <row r="403" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C403" s="145"/>
-      <c r="D403" s="145"/>
-      <c r="E403" s="145"/>
-      <c r="F403" s="145"/>
+      <c r="C403" s="144"/>
+      <c r="D403" s="144"/>
+      <c r="E403" s="144"/>
+      <c r="F403" s="144"/>
     </row>
     <row r="404" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C404" s="145"/>
-      <c r="D404" s="145"/>
-      <c r="E404" s="145"/>
-      <c r="F404" s="145"/>
+      <c r="C404" s="144"/>
+      <c r="D404" s="144"/>
+      <c r="E404" s="144"/>
+      <c r="F404" s="144"/>
     </row>
     <row r="405" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C405" s="145"/>
-      <c r="D405" s="145"/>
-      <c r="E405" s="145"/>
-      <c r="F405" s="145"/>
+      <c r="C405" s="144"/>
+      <c r="D405" s="144"/>
+      <c r="E405" s="144"/>
+      <c r="F405" s="144"/>
     </row>
     <row r="406" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C406" s="145"/>
-      <c r="D406" s="145"/>
-      <c r="E406" s="145"/>
-      <c r="F406" s="145"/>
+      <c r="C406" s="144"/>
+      <c r="D406" s="144"/>
+      <c r="E406" s="144"/>
+      <c r="F406" s="144"/>
     </row>
     <row r="407" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C407" s="145"/>
-      <c r="D407" s="145"/>
-      <c r="E407" s="145"/>
-      <c r="F407" s="145"/>
+      <c r="C407" s="144"/>
+      <c r="D407" s="144"/>
+      <c r="E407" s="144"/>
+      <c r="F407" s="144"/>
     </row>
     <row r="408" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C408" s="145"/>
-      <c r="D408" s="145"/>
-      <c r="E408" s="145"/>
-      <c r="F408" s="145"/>
+      <c r="C408" s="144"/>
+      <c r="D408" s="144"/>
+      <c r="E408" s="144"/>
+      <c r="F408" s="144"/>
     </row>
     <row r="409" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C409" s="145"/>
-      <c r="D409" s="145"/>
-      <c r="E409" s="145"/>
-      <c r="F409" s="145"/>
+      <c r="C409" s="144"/>
+      <c r="D409" s="144"/>
+      <c r="E409" s="144"/>
+      <c r="F409" s="144"/>
     </row>
     <row r="410" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C410" s="145"/>
-      <c r="D410" s="145"/>
-      <c r="E410" s="145"/>
-      <c r="F410" s="145"/>
+      <c r="C410" s="144"/>
+      <c r="D410" s="144"/>
+      <c r="E410" s="144"/>
+      <c r="F410" s="144"/>
     </row>
     <row r="411" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C411" s="145"/>
-      <c r="D411" s="145"/>
-      <c r="E411" s="145"/>
-      <c r="F411" s="145"/>
+      <c r="C411" s="144"/>
+      <c r="D411" s="144"/>
+      <c r="E411" s="144"/>
+      <c r="F411" s="144"/>
     </row>
     <row r="412" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C412" s="145"/>
-      <c r="D412" s="145"/>
-      <c r="E412" s="145"/>
-      <c r="F412" s="145"/>
+      <c r="C412" s="144"/>
+      <c r="D412" s="144"/>
+      <c r="E412" s="144"/>
+      <c r="F412" s="144"/>
     </row>
     <row r="413" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C413" s="145"/>
-      <c r="D413" s="145"/>
-      <c r="E413" s="145"/>
-      <c r="F413" s="145"/>
+      <c r="C413" s="144"/>
+      <c r="D413" s="144"/>
+      <c r="E413" s="144"/>
+      <c r="F413" s="144"/>
     </row>
     <row r="414" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C414" s="145"/>
-      <c r="D414" s="145"/>
-      <c r="E414" s="145"/>
-      <c r="F414" s="145"/>
+      <c r="C414" s="144"/>
+      <c r="D414" s="144"/>
+      <c r="E414" s="144"/>
+      <c r="F414" s="144"/>
     </row>
     <row r="415" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C415" s="145"/>
-      <c r="D415" s="145"/>
-      <c r="E415" s="145"/>
-      <c r="F415" s="145"/>
+      <c r="C415" s="144"/>
+      <c r="D415" s="144"/>
+      <c r="E415" s="144"/>
+      <c r="F415" s="144"/>
     </row>
     <row r="416" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C416" s="145"/>
-      <c r="D416" s="145"/>
-      <c r="E416" s="145"/>
-      <c r="F416" s="145"/>
+      <c r="C416" s="144"/>
+      <c r="D416" s="144"/>
+      <c r="E416" s="144"/>
+      <c r="F416" s="144"/>
     </row>
     <row r="417" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C417" s="145"/>
-      <c r="D417" s="145"/>
-      <c r="E417" s="145"/>
-      <c r="F417" s="145"/>
+      <c r="C417" s="144"/>
+      <c r="D417" s="144"/>
+      <c r="E417" s="144"/>
+      <c r="F417" s="144"/>
     </row>
     <row r="418" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C418" s="145"/>
-      <c r="D418" s="145"/>
-      <c r="E418" s="145"/>
-      <c r="F418" s="145"/>
+      <c r="C418" s="144"/>
+      <c r="D418" s="144"/>
+      <c r="E418" s="144"/>
+      <c r="F418" s="144"/>
     </row>
     <row r="419" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C419" s="145"/>
-      <c r="D419" s="145"/>
-      <c r="E419" s="145"/>
-      <c r="F419" s="145"/>
+      <c r="C419" s="144"/>
+      <c r="D419" s="144"/>
+      <c r="E419" s="144"/>
+      <c r="F419" s="144"/>
     </row>
     <row r="420" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C420" s="145"/>
-      <c r="D420" s="145"/>
-      <c r="E420" s="145"/>
-      <c r="F420" s="145"/>
+      <c r="C420" s="144"/>
+      <c r="D420" s="144"/>
+      <c r="E420" s="144"/>
+      <c r="F420" s="144"/>
     </row>
     <row r="421" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C421" s="145"/>
-      <c r="D421" s="145"/>
-      <c r="E421" s="145"/>
-      <c r="F421" s="145"/>
+      <c r="C421" s="144"/>
+      <c r="D421" s="144"/>
+      <c r="E421" s="144"/>
+      <c r="F421" s="144"/>
     </row>
     <row r="422" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C422" s="145"/>
-      <c r="D422" s="145"/>
-      <c r="E422" s="145"/>
-      <c r="F422" s="145"/>
+      <c r="C422" s="144"/>
+      <c r="D422" s="144"/>
+      <c r="E422" s="144"/>
+      <c r="F422" s="144"/>
     </row>
     <row r="423" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C423" s="145"/>
-      <c r="D423" s="145"/>
-      <c r="E423" s="145"/>
-      <c r="F423" s="145"/>
+      <c r="C423" s="144"/>
+      <c r="D423" s="144"/>
+      <c r="E423" s="144"/>
+      <c r="F423" s="144"/>
     </row>
     <row r="424" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C424" s="145"/>
-      <c r="D424" s="145"/>
-      <c r="E424" s="145"/>
-      <c r="F424" s="145"/>
+      <c r="C424" s="144"/>
+      <c r="D424" s="144"/>
+      <c r="E424" s="144"/>
+      <c r="F424" s="144"/>
     </row>
     <row r="425" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C425" s="145"/>
-      <c r="D425" s="145"/>
-      <c r="E425" s="145"/>
-      <c r="F425" s="145"/>
+      <c r="C425" s="144"/>
+      <c r="D425" s="144"/>
+      <c r="E425" s="144"/>
+      <c r="F425" s="144"/>
     </row>
     <row r="426" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C426" s="145"/>
-      <c r="D426" s="145"/>
-      <c r="E426" s="145"/>
-      <c r="F426" s="145"/>
+      <c r="C426" s="144"/>
+      <c r="D426" s="144"/>
+      <c r="E426" s="144"/>
+      <c r="F426" s="144"/>
     </row>
     <row r="427" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C427" s="145"/>
-      <c r="D427" s="145"/>
-      <c r="E427" s="145"/>
-      <c r="F427" s="145"/>
+      <c r="C427" s="144"/>
+      <c r="D427" s="144"/>
+      <c r="E427" s="144"/>
+      <c r="F427" s="144"/>
     </row>
     <row r="428" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C428" s="145"/>
-      <c r="D428" s="145"/>
-      <c r="E428" s="145"/>
-      <c r="F428" s="145"/>
+      <c r="C428" s="144"/>
+      <c r="D428" s="144"/>
+      <c r="E428" s="144"/>
+      <c r="F428" s="144"/>
     </row>
     <row r="429" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C429" s="145"/>
-      <c r="D429" s="145"/>
-      <c r="E429" s="145"/>
-      <c r="F429" s="145"/>
+      <c r="C429" s="144"/>
+      <c r="D429" s="144"/>
+      <c r="E429" s="144"/>
+      <c r="F429" s="144"/>
     </row>
     <row r="430" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C430" s="145"/>
-      <c r="D430" s="145"/>
-      <c r="E430" s="145"/>
-      <c r="F430" s="145"/>
+      <c r="C430" s="144"/>
+      <c r="D430" s="144"/>
+      <c r="E430" s="144"/>
+      <c r="F430" s="144"/>
     </row>
     <row r="431" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C431" s="145"/>
-      <c r="D431" s="145"/>
-      <c r="E431" s="145"/>
-      <c r="F431" s="145"/>
+      <c r="C431" s="144"/>
+      <c r="D431" s="144"/>
+      <c r="E431" s="144"/>
+      <c r="F431" s="144"/>
     </row>
     <row r="432" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C432" s="145"/>
-      <c r="D432" s="145"/>
-      <c r="E432" s="145"/>
-      <c r="F432" s="145"/>
+      <c r="C432" s="144"/>
+      <c r="D432" s="144"/>
+      <c r="E432" s="144"/>
+      <c r="F432" s="144"/>
     </row>
     <row r="433" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C433" s="145"/>
-      <c r="D433" s="145"/>
-      <c r="E433" s="145"/>
-      <c r="F433" s="145"/>
+      <c r="C433" s="144"/>
+      <c r="D433" s="144"/>
+      <c r="E433" s="144"/>
+      <c r="F433" s="144"/>
     </row>
     <row r="434" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C434" s="145"/>
-      <c r="D434" s="145"/>
-      <c r="E434" s="145"/>
-      <c r="F434" s="145"/>
+      <c r="C434" s="144"/>
+      <c r="D434" s="144"/>
+      <c r="E434" s="144"/>
+      <c r="F434" s="144"/>
     </row>
     <row r="435" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C435" s="145"/>
-      <c r="D435" s="145"/>
-      <c r="E435" s="145"/>
-      <c r="F435" s="145"/>
+      <c r="C435" s="144"/>
+      <c r="D435" s="144"/>
+      <c r="E435" s="144"/>
+      <c r="F435" s="144"/>
     </row>
     <row r="436" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C436" s="145"/>
-      <c r="D436" s="145"/>
-      <c r="E436" s="145"/>
-      <c r="F436" s="145"/>
+      <c r="C436" s="144"/>
+      <c r="D436" s="144"/>
+      <c r="E436" s="144"/>
+      <c r="F436" s="144"/>
     </row>
     <row r="437" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C437" s="145"/>
-      <c r="D437" s="145"/>
-      <c r="E437" s="145"/>
-      <c r="F437" s="145"/>
+      <c r="C437" s="144"/>
+      <c r="D437" s="144"/>
+      <c r="E437" s="144"/>
+      <c r="F437" s="144"/>
     </row>
     <row r="438" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C438" s="145"/>
-      <c r="D438" s="145"/>
-      <c r="E438" s="145"/>
-      <c r="F438" s="145"/>
+      <c r="C438" s="144"/>
+      <c r="D438" s="144"/>
+      <c r="E438" s="144"/>
+      <c r="F438" s="144"/>
     </row>
     <row r="439" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C439" s="145"/>
-      <c r="D439" s="145"/>
-      <c r="E439" s="145"/>
-      <c r="F439" s="145"/>
+      <c r="C439" s="144"/>
+      <c r="D439" s="144"/>
+      <c r="E439" s="144"/>
+      <c r="F439" s="144"/>
     </row>
     <row r="440" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C440" s="145"/>
-      <c r="D440" s="145"/>
-      <c r="E440" s="145"/>
-      <c r="F440" s="145"/>
+      <c r="C440" s="144"/>
+      <c r="D440" s="144"/>
+      <c r="E440" s="144"/>
+      <c r="F440" s="144"/>
     </row>
     <row r="441" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C441" s="145"/>
-      <c r="D441" s="145"/>
-      <c r="E441" s="145"/>
-      <c r="F441" s="145"/>
+      <c r="C441" s="144"/>
+      <c r="D441" s="144"/>
+      <c r="E441" s="144"/>
+      <c r="F441" s="144"/>
     </row>
     <row r="442" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C442" s="145"/>
-      <c r="D442" s="145"/>
-      <c r="E442" s="145"/>
-      <c r="F442" s="145"/>
+      <c r="C442" s="144"/>
+      <c r="D442" s="144"/>
+      <c r="E442" s="144"/>
+      <c r="F442" s="144"/>
     </row>
     <row r="443" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C443" s="145"/>
-      <c r="D443" s="145"/>
-      <c r="E443" s="145"/>
-      <c r="F443" s="145"/>
+      <c r="C443" s="144"/>
+      <c r="D443" s="144"/>
+      <c r="E443" s="144"/>
+      <c r="F443" s="144"/>
     </row>
     <row r="444" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C444" s="145"/>
-      <c r="D444" s="145"/>
-      <c r="E444" s="145"/>
-      <c r="F444" s="145"/>
+      <c r="C444" s="144"/>
+      <c r="D444" s="144"/>
+      <c r="E444" s="144"/>
+      <c r="F444" s="144"/>
     </row>
     <row r="445" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C445" s="145"/>
-      <c r="D445" s="145"/>
-      <c r="E445" s="145"/>
-      <c r="F445" s="145"/>
+      <c r="C445" s="144"/>
+      <c r="D445" s="144"/>
+      <c r="E445" s="144"/>
+      <c r="F445" s="144"/>
     </row>
     <row r="446" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C446" s="145"/>
-      <c r="D446" s="145"/>
-      <c r="E446" s="145"/>
-      <c r="F446" s="145"/>
+      <c r="C446" s="144"/>
+      <c r="D446" s="144"/>
+      <c r="E446" s="144"/>
+      <c r="F446" s="144"/>
     </row>
     <row r="447" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C447" s="145"/>
-      <c r="D447" s="145"/>
-      <c r="E447" s="145"/>
-      <c r="F447" s="145"/>
+      <c r="C447" s="144"/>
+      <c r="D447" s="144"/>
+      <c r="E447" s="144"/>
+      <c r="F447" s="144"/>
     </row>
     <row r="448" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C448" s="145"/>
-      <c r="D448" s="145"/>
-      <c r="E448" s="145"/>
-      <c r="F448" s="145"/>
+      <c r="C448" s="144"/>
+      <c r="D448" s="144"/>
+      <c r="E448" s="144"/>
+      <c r="F448" s="144"/>
     </row>
     <row r="449" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C449" s="145"/>
-      <c r="D449" s="145"/>
-      <c r="E449" s="145"/>
-      <c r="F449" s="145"/>
+      <c r="C449" s="144"/>
+      <c r="D449" s="144"/>
+      <c r="E449" s="144"/>
+      <c r="F449" s="144"/>
     </row>
     <row r="450" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C450" s="145"/>
-      <c r="D450" s="145"/>
-      <c r="E450" s="145"/>
-      <c r="F450" s="145"/>
+      <c r="C450" s="144"/>
+      <c r="D450" s="144"/>
+      <c r="E450" s="144"/>
+      <c r="F450" s="144"/>
     </row>
     <row r="451" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C451" s="145"/>
-      <c r="D451" s="145"/>
-      <c r="E451" s="145"/>
-      <c r="F451" s="145"/>
+      <c r="C451" s="144"/>
+      <c r="D451" s="144"/>
+      <c r="E451" s="144"/>
+      <c r="F451" s="144"/>
     </row>
     <row r="452" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C452" s="145"/>
-      <c r="D452" s="145"/>
-      <c r="E452" s="145"/>
-      <c r="F452" s="145"/>
+      <c r="C452" s="144"/>
+      <c r="D452" s="144"/>
+      <c r="E452" s="144"/>
+      <c r="F452" s="144"/>
     </row>
     <row r="453" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C453" s="145"/>
-      <c r="D453" s="145"/>
-      <c r="E453" s="145"/>
-      <c r="F453" s="145"/>
+      <c r="C453" s="144"/>
+      <c r="D453" s="144"/>
+      <c r="E453" s="144"/>
+      <c r="F453" s="144"/>
     </row>
     <row r="454" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C454" s="145"/>
-      <c r="D454" s="145"/>
-      <c r="E454" s="145"/>
-      <c r="F454" s="145"/>
+      <c r="C454" s="144"/>
+      <c r="D454" s="144"/>
+      <c r="E454" s="144"/>
+      <c r="F454" s="144"/>
     </row>
     <row r="455" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C455" s="145"/>
-      <c r="D455" s="145"/>
-      <c r="E455" s="145"/>
-      <c r="F455" s="145"/>
+      <c r="C455" s="144"/>
+      <c r="D455" s="144"/>
+      <c r="E455" s="144"/>
+      <c r="F455" s="144"/>
     </row>
     <row r="456" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C456" s="145"/>
-      <c r="D456" s="145"/>
-      <c r="E456" s="145"/>
-      <c r="F456" s="145"/>
+      <c r="C456" s="144"/>
+      <c r="D456" s="144"/>
+      <c r="E456" s="144"/>
+      <c r="F456" s="144"/>
     </row>
     <row r="457" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C457" s="145"/>
-      <c r="D457" s="145"/>
-      <c r="E457" s="145"/>
-      <c r="F457" s="145"/>
+      <c r="C457" s="144"/>
+      <c r="D457" s="144"/>
+      <c r="E457" s="144"/>
+      <c r="F457" s="144"/>
     </row>
     <row r="458" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C458" s="145"/>
-      <c r="D458" s="145"/>
-      <c r="E458" s="145"/>
-      <c r="F458" s="145"/>
+      <c r="C458" s="144"/>
+      <c r="D458" s="144"/>
+      <c r="E458" s="144"/>
+      <c r="F458" s="144"/>
     </row>
     <row r="459" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C459" s="145"/>
-      <c r="D459" s="145"/>
-      <c r="E459" s="145"/>
-      <c r="F459" s="145"/>
+      <c r="C459" s="144"/>
+      <c r="D459" s="144"/>
+      <c r="E459" s="144"/>
+      <c r="F459" s="144"/>
     </row>
     <row r="460" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C460" s="145"/>
-      <c r="D460" s="145"/>
-      <c r="E460" s="145"/>
-      <c r="F460" s="145"/>
+      <c r="C460" s="144"/>
+      <c r="D460" s="144"/>
+      <c r="E460" s="144"/>
+      <c r="F460" s="144"/>
     </row>
     <row r="461" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C461" s="145"/>
-      <c r="D461" s="145"/>
-      <c r="E461" s="145"/>
-      <c r="F461" s="145"/>
+      <c r="C461" s="144"/>
+      <c r="D461" s="144"/>
+      <c r="E461" s="144"/>
+      <c r="F461" s="144"/>
     </row>
     <row r="462" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C462" s="145"/>
-      <c r="D462" s="145"/>
-      <c r="E462" s="145"/>
-      <c r="F462" s="145"/>
+      <c r="C462" s="144"/>
+      <c r="D462" s="144"/>
+      <c r="E462" s="144"/>
+      <c r="F462" s="144"/>
     </row>
     <row r="463" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C463" s="145"/>
-      <c r="D463" s="145"/>
-      <c r="E463" s="145"/>
-      <c r="F463" s="145"/>
+      <c r="C463" s="144"/>
+      <c r="D463" s="144"/>
+      <c r="E463" s="144"/>
+      <c r="F463" s="144"/>
     </row>
     <row r="464" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C464" s="145"/>
-      <c r="D464" s="145"/>
-      <c r="E464" s="145"/>
-      <c r="F464" s="145"/>
+      <c r="C464" s="144"/>
+      <c r="D464" s="144"/>
+      <c r="E464" s="144"/>
+      <c r="F464" s="144"/>
     </row>
     <row r="465" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C465" s="145"/>
-      <c r="D465" s="145"/>
-      <c r="E465" s="145"/>
-      <c r="F465" s="145"/>
+      <c r="C465" s="144"/>
+      <c r="D465" s="144"/>
+      <c r="E465" s="144"/>
+      <c r="F465" s="144"/>
     </row>
     <row r="466" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C466" s="145"/>
-      <c r="D466" s="145"/>
-      <c r="E466" s="145"/>
-      <c r="F466" s="145"/>
+      <c r="C466" s="144"/>
+      <c r="D466" s="144"/>
+      <c r="E466" s="144"/>
+      <c r="F466" s="144"/>
     </row>
     <row r="467" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C467" s="145"/>
-      <c r="D467" s="145"/>
-      <c r="E467" s="145"/>
-      <c r="F467" s="145"/>
+      <c r="C467" s="144"/>
+      <c r="D467" s="144"/>
+      <c r="E467" s="144"/>
+      <c r="F467" s="144"/>
     </row>
     <row r="468" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C468" s="145"/>
-      <c r="D468" s="145"/>
-      <c r="E468" s="145"/>
-      <c r="F468" s="145"/>
+      <c r="C468" s="144"/>
+      <c r="D468" s="144"/>
+      <c r="E468" s="144"/>
+      <c r="F468" s="144"/>
     </row>
     <row r="469" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C469" s="145"/>
-      <c r="D469" s="145"/>
-      <c r="E469" s="145"/>
-      <c r="F469" s="145"/>
+      <c r="C469" s="144"/>
+      <c r="D469" s="144"/>
+      <c r="E469" s="144"/>
+      <c r="F469" s="144"/>
     </row>
     <row r="470" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C470" s="145"/>
-      <c r="D470" s="145"/>
-      <c r="E470" s="145"/>
-      <c r="F470" s="145"/>
+      <c r="C470" s="144"/>
+      <c r="D470" s="144"/>
+      <c r="E470" s="144"/>
+      <c r="F470" s="144"/>
     </row>
     <row r="471" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C471" s="145"/>
-      <c r="D471" s="145"/>
-      <c r="E471" s="145"/>
-      <c r="F471" s="145"/>
+      <c r="C471" s="144"/>
+      <c r="D471" s="144"/>
+      <c r="E471" s="144"/>
+      <c r="F471" s="144"/>
     </row>
     <row r="472" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C472" s="145"/>
-      <c r="D472" s="145"/>
-      <c r="E472" s="145"/>
-      <c r="F472" s="145"/>
+      <c r="C472" s="144"/>
+      <c r="D472" s="144"/>
+      <c r="E472" s="144"/>
+      <c r="F472" s="144"/>
     </row>
     <row r="473" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C473" s="145"/>
-      <c r="D473" s="145"/>
-      <c r="E473" s="145"/>
-      <c r="F473" s="145"/>
+      <c r="C473" s="144"/>
+      <c r="D473" s="144"/>
+      <c r="E473" s="144"/>
+      <c r="F473" s="144"/>
     </row>
     <row r="474" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C474" s="145"/>
-      <c r="D474" s="145"/>
-      <c r="E474" s="145"/>
-      <c r="F474" s="145"/>
+      <c r="C474" s="144"/>
+      <c r="D474" s="144"/>
+      <c r="E474" s="144"/>
+      <c r="F474" s="144"/>
     </row>
     <row r="475" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C475" s="145"/>
-      <c r="D475" s="145"/>
-      <c r="E475" s="145"/>
-      <c r="F475" s="145"/>
+      <c r="C475" s="144"/>
+      <c r="D475" s="144"/>
+      <c r="E475" s="144"/>
+      <c r="F475" s="144"/>
     </row>
     <row r="476" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C476" s="145"/>
-      <c r="D476" s="145"/>
-      <c r="E476" s="145"/>
-      <c r="F476" s="145"/>
+      <c r="C476" s="144"/>
+      <c r="D476" s="144"/>
+      <c r="E476" s="144"/>
+      <c r="F476" s="144"/>
     </row>
     <row r="477" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C477" s="145"/>
-      <c r="D477" s="145"/>
-      <c r="E477" s="145"/>
-      <c r="F477" s="145"/>
+      <c r="C477" s="144"/>
+      <c r="D477" s="144"/>
+      <c r="E477" s="144"/>
+      <c r="F477" s="144"/>
     </row>
     <row r="478" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C478" s="145"/>
-      <c r="D478" s="145"/>
-      <c r="E478" s="145"/>
-      <c r="F478" s="145"/>
+      <c r="C478" s="144"/>
+      <c r="D478" s="144"/>
+      <c r="E478" s="144"/>
+      <c r="F478" s="144"/>
     </row>
     <row r="479" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C479" s="145"/>
-      <c r="D479" s="145"/>
-      <c r="E479" s="145"/>
-      <c r="F479" s="145"/>
+      <c r="C479" s="144"/>
+      <c r="D479" s="144"/>
+      <c r="E479" s="144"/>
+      <c r="F479" s="144"/>
     </row>
     <row r="480" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C480" s="145"/>
-      <c r="D480" s="145"/>
-      <c r="E480" s="145"/>
-      <c r="F480" s="145"/>
+      <c r="C480" s="144"/>
+      <c r="D480" s="144"/>
+      <c r="E480" s="144"/>
+      <c r="F480" s="144"/>
     </row>
     <row r="481" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C481" s="145"/>
-      <c r="D481" s="145"/>
-      <c r="E481" s="145"/>
-      <c r="F481" s="145"/>
+      <c r="C481" s="144"/>
+      <c r="D481" s="144"/>
+      <c r="E481" s="144"/>
+      <c r="F481" s="144"/>
     </row>
     <row r="482" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C482" s="145"/>
-      <c r="D482" s="145"/>
-      <c r="E482" s="145"/>
-      <c r="F482" s="145"/>
+      <c r="C482" s="144"/>
+      <c r="D482" s="144"/>
+      <c r="E482" s="144"/>
+      <c r="F482" s="144"/>
     </row>
     <row r="483" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C483" s="145"/>
-      <c r="D483" s="145"/>
-      <c r="E483" s="145"/>
-      <c r="F483" s="145"/>
+      <c r="C483" s="144"/>
+      <c r="D483" s="144"/>
+      <c r="E483" s="144"/>
+      <c r="F483" s="144"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/source/STC_Textblocs_Source.xlsx
+++ b/source/STC_Textblocs_Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stctravel-my.sharepoint.com/personal/clemens_bartlome_stc_ch/Documents/12_Development/github/TextblocsOutlook/TextblocsOutlookAddIn/source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stctravel-my.sharepoint.com/personal/clemens_bartlome_stc_ch/Documents/12_Development/github/STC/TextBlocsAddIn/TextblocsOutlookAddIn/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="416" documentId="8_{94B17F8A-FB08-44EE-9220-44A499DEE7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F73AF7A2-5166-4AAF-8B94-71AB78587331}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB384661-ED36-4426-94BD-E4DFDF837984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99471E66-6148-4C96-BA12-0B3DC411200A}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{99471E66-6148-4C96-BA12-0B3DC411200A}"/>
   </bookViews>
   <sheets>
     <sheet name="Template Outlook" sheetId="1" r:id="rId1"/>
@@ -3257,7 +3257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3519,16 +3519,7 @@
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3552,10 +3543,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4387,13 +4374,13 @@
       <c r="C27" s="46" t="s">
         <v>248</v>
       </c>
-      <c r="D27" s="90" t="s">
+      <c r="D27" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="E27" s="90" t="s">
+      <c r="E27" s="89" t="s">
         <v>250</v>
       </c>
-      <c r="F27" s="90" t="s">
+      <c r="F27" s="89" t="s">
         <v>251</v>
       </c>
     </row>
@@ -4444,16 +4431,16 @@
       <c r="B30" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="89" t="s">
+      <c r="C30" s="73" t="s">
         <v>229</v>
       </c>
-      <c r="D30" s="89" t="s">
+      <c r="D30" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="E30" s="89" t="s">
+      <c r="E30" s="73" t="s">
         <v>256</v>
       </c>
-      <c r="F30" s="89" t="s">
+      <c r="F30" s="73" t="s">
         <v>257</v>
       </c>
     </row>
@@ -4467,7 +4454,7 @@
       <c r="C31" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="D31" s="91" t="s">
+      <c r="D31" s="29" t="s">
         <v>259</v>
       </c>
       <c r="E31" s="29" t="s">
@@ -4541,13 +4528,13 @@
       <c r="C35" s="56" t="s">
         <v>266</v>
       </c>
-      <c r="D35" s="92" t="s">
+      <c r="D35" s="57" t="s">
         <v>267</v>
       </c>
-      <c r="E35" s="92" t="s">
+      <c r="E35" s="57" t="s">
         <v>268</v>
       </c>
-      <c r="F35" s="92" t="s">
+      <c r="F35" s="57" t="s">
         <v>269</v>
       </c>
     </row>
@@ -4799,13 +4786,13 @@
       <c r="C48" s="87" t="s">
         <v>133</v>
       </c>
-      <c r="D48" s="93" t="s">
+      <c r="D48" s="90" t="s">
         <v>302</v>
       </c>
-      <c r="E48" s="94" t="s">
+      <c r="E48" s="91" t="s">
         <v>303</v>
       </c>
-      <c r="F48" s="94" t="s">
+      <c r="F48" s="91" t="s">
         <v>304</v>
       </c>
     </row>
